--- a/src/PE1VM1/App/MET/IpcApplication/Vom/Alert/matrix/scc/alert_B_WASLEV-CSTD-0-01-B-C1.xlsx
+++ b/src/PE1VM1/App/MET/IpcApplication/Vom/Alert/matrix/scc/alert_B_WASLEV-CSTD-0-01-B-C1.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27928"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="26731"/>
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\work\10_mcu\19epfv3_mcu_app_mainline\src\IpcApplication\Vom\Alert\matrix\scc\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\_JPlaptop\BEV_MCU\git_v043_AlertFix\src\PE1VM1\App\MET\IpcApplication\Vom\Alert\matrix\scc\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E79558B4-2AA1-4D12-BC98-D58EF103D024}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2B03DED3-A159-46FD-8BC9-4F52D97B2F90}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-7575" yWindow="-16320" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-14265" yWindow="-16320" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="表紙（承認欄）" sheetId="18" r:id="rId1"/>
@@ -1051,7 +1051,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3641" uniqueCount="420">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3646" uniqueCount="423">
   <si>
     <t>更新履歴</t>
     <phoneticPr fontId="2"/>
@@ -2956,9 +2956,6 @@
     <phoneticPr fontId="2"/>
   </si>
   <si>
-    <t>○</t>
-  </si>
-  <si>
     <t>入力</t>
     <phoneticPr fontId="2"/>
   </si>
@@ -4240,9 +4237,6 @@
     <phoneticPr fontId="2"/>
   </si>
   <si>
-    <t>(株)NTTデータMSE</t>
-  </si>
-  <si>
     <t>承認</t>
     <rPh sb="0" eb="2">
       <t>ショウニン</t>
@@ -4378,6 +4372,34 @@
 ALERT_B_WASLEV_WASHLVSW_SGNL_**
 ALERT_B_WASLEV_DLY_CNT_**
 ALERT_B_WASLEV_JDG_**</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>1.6.2</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>DTPH Kiko</t>
+  </si>
+  <si>
+    <t>－</t>
+  </si>
+  <si>
+    <t>(株)デンソー</t>
+  </si>
+  <si>
+    <t>BEVシス検ADAS
+課題対応（BEV3CDCMET-2941）
+[Matrix]シート
+・RWの記載を変更（○→ー）
+[CH_Design]シート
+・RWの記載を変更（WASH→ー）</t>
+    <rPh sb="11" eb="13">
+      <t>カダイ</t>
+    </rPh>
+    <rPh sb="13" eb="15">
+      <t>タイオウ</t>
+    </rPh>
     <phoneticPr fontId="2"/>
   </si>
 </sst>
@@ -4771,7 +4793,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="85">
+  <borders count="87">
     <border>
       <left/>
       <right/>
@@ -5869,6 +5891,32 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
@@ -5881,7 +5929,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="346">
+  <cellXfs count="353">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -6728,6 +6776,27 @@
     <xf numFmtId="14" fontId="0" fillId="0" borderId="78" xfId="0" applyNumberFormat="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="62" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="62" xfId="0" applyNumberFormat="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="85" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="62" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="62" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="63" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="18" fillId="0" borderId="86" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="27" fillId="0" borderId="27" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -7237,16 +7306,16 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>38</xdr:col>
-      <xdr:colOff>100782</xdr:colOff>
+      <xdr:colOff>134399</xdr:colOff>
       <xdr:row>55</xdr:row>
-      <xdr:rowOff>100782</xdr:rowOff>
+      <xdr:rowOff>107132</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="6" name="図 5">
+        <xdr:cNvPr id="7" name="図 6">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{436E07AB-C8E6-4332-BDBC-42B250368296}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F8656157-BDAB-C86F-6682-BD8EF437B460}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -7262,8 +7331,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="5667375" y="8420100"/>
-          <a:ext cx="586557" cy="586557"/>
+          <a:off x="5098676" y="8157882"/>
+          <a:ext cx="571429" cy="571429"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -17556,17 +17625,17 @@
       <sheetName val="４．ナビモデル"/>
       <sheetName val="３．サウンドモデル"/>
       <sheetName val="２．ラジオモデル"/>
+      <sheetName val="1.概述"/>
       <sheetName val="V200複合試験_担当分け_(2)1"/>
       <sheetName val="Spec_List_(19MC-DCM)_1"/>
       <sheetName val="Cooling_Unit"/>
-      <sheetName val="1.概述"/>
       <sheetName val="OpenIssueList"/>
-      <sheetName val="PullDown"/>
       <sheetName val="ECU基盤"/>
       <sheetName val="Name2"/>
       <sheetName val="Name3"/>
       <sheetName val="Company"/>
       <sheetName val="Name"/>
+      <sheetName val="PullDown"/>
       <sheetName val="エンジン型式"/>
       <sheetName val="分类数据"/>
       <sheetName val="index"/>
@@ -17598,6 +17667,37 @@
       <sheetName val="改訂履歴"/>
       <sheetName val="Sheet1"/>
       <sheetName val="⑥フューエル"/>
+      <sheetName val="STEP1-Definition"/>
+      <sheetName val="No.31"/>
+      <sheetName val="階層一覧"/>
+      <sheetName val="测试计划"/>
+      <sheetName val="2.2.4_起動終了時"/>
+      <sheetName val="全戻りﾊﾞｸﾞ"/>
+      <sheetName val="DataShare"/>
+      <sheetName val="ＯＰＭ設備"/>
+      <sheetName val="償却計算"/>
+      <sheetName val="技術費"/>
+      <sheetName val="消耗材"/>
+      <sheetName val="生産用消耗工具費"/>
+      <sheetName val="投資込みＭＪ原価"/>
+      <sheetName val="ＭＪ加工費"/>
+      <sheetName val="仕損根拠"/>
+      <sheetName val="DetailSequence"/>
+      <sheetName val="ERRＩＤ90"/>
+      <sheetName val="vocabulary"/>
+      <sheetName val="Calibration"/>
+      <sheetName val="CVBS"/>
+      <sheetName val="RGB"/>
+      <sheetName val="調査シート"/>
+      <sheetName val="SCH"/>
+      <sheetName val="发行控制"/>
+      <sheetName val="Vibrate test"/>
+      <sheetName val="Data"/>
+      <sheetName val="注釈"/>
+      <sheetName val="仕向け決定用情報取得(GM250)"/>
+      <sheetName val="付録①（GM用）"/>
+      <sheetName val="Data.Share"/>
+      <sheetName val="Func.Share"/>
     </sheetNames>
     <sheetDataSet>
       <sheetData sheetId="0" refreshError="1"/>
@@ -17678,10 +17778,10 @@
       <sheetData sheetId="57" refreshError="1"/>
       <sheetData sheetId="58" refreshError="1"/>
       <sheetData sheetId="59" refreshError="1"/>
-      <sheetData sheetId="60"/>
+      <sheetData sheetId="60" refreshError="1"/>
       <sheetData sheetId="61"/>
       <sheetData sheetId="62"/>
-      <sheetData sheetId="63" refreshError="1"/>
+      <sheetData sheetId="63"/>
       <sheetData sheetId="64" refreshError="1"/>
       <sheetData sheetId="65" refreshError="1"/>
       <sheetData sheetId="66" refreshError="1"/>
@@ -17720,6 +17820,37 @@
       <sheetData sheetId="99" refreshError="1"/>
       <sheetData sheetId="100" refreshError="1"/>
       <sheetData sheetId="101" refreshError="1"/>
+      <sheetData sheetId="102" refreshError="1"/>
+      <sheetData sheetId="103" refreshError="1"/>
+      <sheetData sheetId="104" refreshError="1"/>
+      <sheetData sheetId="105" refreshError="1"/>
+      <sheetData sheetId="106" refreshError="1"/>
+      <sheetData sheetId="107" refreshError="1"/>
+      <sheetData sheetId="108" refreshError="1"/>
+      <sheetData sheetId="109" refreshError="1"/>
+      <sheetData sheetId="110" refreshError="1"/>
+      <sheetData sheetId="111" refreshError="1"/>
+      <sheetData sheetId="112" refreshError="1"/>
+      <sheetData sheetId="113" refreshError="1"/>
+      <sheetData sheetId="114" refreshError="1"/>
+      <sheetData sheetId="115" refreshError="1"/>
+      <sheetData sheetId="116" refreshError="1"/>
+      <sheetData sheetId="117" refreshError="1"/>
+      <sheetData sheetId="118" refreshError="1"/>
+      <sheetData sheetId="119" refreshError="1"/>
+      <sheetData sheetId="120" refreshError="1"/>
+      <sheetData sheetId="121" refreshError="1"/>
+      <sheetData sheetId="122" refreshError="1"/>
+      <sheetData sheetId="123" refreshError="1"/>
+      <sheetData sheetId="124" refreshError="1"/>
+      <sheetData sheetId="125" refreshError="1"/>
+      <sheetData sheetId="126" refreshError="1"/>
+      <sheetData sheetId="127" refreshError="1"/>
+      <sheetData sheetId="128" refreshError="1"/>
+      <sheetData sheetId="129" refreshError="1"/>
+      <sheetData sheetId="130" refreshError="1"/>
+      <sheetData sheetId="131" refreshError="1"/>
+      <sheetData sheetId="132" refreshError="1"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
@@ -17858,12 +17989,49 @@
       <sheetName val="Config - dspmgr"/>
       <sheetName val="凡例・注記記載用"/>
       <sheetName val="入力パラメータ"/>
-      <sheetName val="原紙"/>
       <sheetName val="マスタテーブル登録データ"/>
       <sheetName val="記入シート"/>
+      <sheetName val="原紙"/>
       <sheetName val="format"/>
       <sheetName val="検査シート"/>
       <sheetName val="1.概述"/>
+      <sheetName val="InterFace"/>
+      <sheetName val="集計表"/>
+      <sheetName val="vocabulary"/>
+      <sheetName val="Calibration"/>
+      <sheetName val="CVBS"/>
+      <sheetName val="RGB"/>
+      <sheetName val="DetailSequence"/>
+      <sheetName val="日程"/>
+      <sheetName val="進捗"/>
+      <sheetName val="印刷"/>
+      <sheetName val="★ONS_MSG_list"/>
+      <sheetName val="Defined Layout Screen_Ver.0.6"/>
+      <sheetName val="ｲﾝﾊﾟｸﾄ影響台数集計表"/>
+      <sheetName val="実勢(売上)台数表"/>
+      <sheetName val="月別企画台数表"/>
+      <sheetName val="プロジェクト一覧表(現行)"/>
+      <sheetName val="限界利益表(半期別)"/>
+      <sheetName val="機種マスタ"/>
+      <sheetName val="機種ﾏｽﾀ（他車）"/>
+      <sheetName val="売上高表(半期別)"/>
+      <sheetName val="地点情報データ応答"/>
+      <sheetName val="階層一覧"/>
+      <sheetName val="リソーセス算出"/>
+      <sheetName val="定義"/>
+      <sheetName val="ドメイン一覧"/>
+      <sheetName val="変更区分一覧"/>
+      <sheetName val="難易度量一覧"/>
+      <sheetName val="ユーザ一覧"/>
+      <sheetName val="Normal(Mark)"/>
+      <sheetName val="リストデータ"/>
+      <sheetName val="②P071中計　工数パターン1312更新"/>
+      <sheetName val="FBtbl"/>
+      <sheetName val="R0-10表紙"/>
+      <sheetName val="入力規則"/>
+      <sheetName val="#REF"/>
+      <sheetName val="Contents"/>
+      <sheetName val="選択肢"/>
     </sheetNames>
     <sheetDataSet>
       <sheetData sheetId="0" refreshError="1"/>
@@ -18007,6 +18175,43 @@
       <sheetData sheetId="132" refreshError="1"/>
       <sheetData sheetId="133" refreshError="1"/>
       <sheetData sheetId="134" refreshError="1"/>
+      <sheetData sheetId="135" refreshError="1"/>
+      <sheetData sheetId="136" refreshError="1"/>
+      <sheetData sheetId="137" refreshError="1"/>
+      <sheetData sheetId="138" refreshError="1"/>
+      <sheetData sheetId="139" refreshError="1"/>
+      <sheetData sheetId="140" refreshError="1"/>
+      <sheetData sheetId="141" refreshError="1"/>
+      <sheetData sheetId="142" refreshError="1"/>
+      <sheetData sheetId="143" refreshError="1"/>
+      <sheetData sheetId="144" refreshError="1"/>
+      <sheetData sheetId="145" refreshError="1"/>
+      <sheetData sheetId="146" refreshError="1"/>
+      <sheetData sheetId="147" refreshError="1"/>
+      <sheetData sheetId="148" refreshError="1"/>
+      <sheetData sheetId="149" refreshError="1"/>
+      <sheetData sheetId="150" refreshError="1"/>
+      <sheetData sheetId="151" refreshError="1"/>
+      <sheetData sheetId="152" refreshError="1"/>
+      <sheetData sheetId="153" refreshError="1"/>
+      <sheetData sheetId="154" refreshError="1"/>
+      <sheetData sheetId="155" refreshError="1"/>
+      <sheetData sheetId="156" refreshError="1"/>
+      <sheetData sheetId="157" refreshError="1"/>
+      <sheetData sheetId="158" refreshError="1"/>
+      <sheetData sheetId="159" refreshError="1"/>
+      <sheetData sheetId="160" refreshError="1"/>
+      <sheetData sheetId="161" refreshError="1"/>
+      <sheetData sheetId="162" refreshError="1"/>
+      <sheetData sheetId="163" refreshError="1"/>
+      <sheetData sheetId="164" refreshError="1"/>
+      <sheetData sheetId="165" refreshError="1"/>
+      <sheetData sheetId="166" refreshError="1"/>
+      <sheetData sheetId="167" refreshError="1"/>
+      <sheetData sheetId="168" refreshError="1"/>
+      <sheetData sheetId="169" refreshError="1"/>
+      <sheetData sheetId="170" refreshError="1"/>
+      <sheetData sheetId="171" refreshError="1"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
@@ -18188,10 +18393,10 @@
       <sheetName val="CPF"/>
       <sheetName val="編集"/>
       <sheetName val="PAIData"/>
+      <sheetName val="⑪1ﾊﾞﾘｴｰｼｮﾝ(16LX)△１"/>
       <sheetName val="NCastalone"/>
       <sheetName val="dongia (2)"/>
       <sheetName val="Volumes"/>
-      <sheetName val="⑪1ﾊﾞﾘｴｰｼｮﾝ(16LX)△１"/>
       <sheetName val="加工費"/>
       <sheetName val="車両仕様 嗼1嗼1噌1鲌"/>
       <sheetName val="車両仕様 勜+勜+匬+鲌"/>
@@ -18201,8 +18406,8 @@
       <sheetName val="Y230"/>
       <sheetName val="MASTER"/>
       <sheetName val="設定"/>
+      <sheetName val="電子ﾎﾞﾘｭｰﾑ設定値（740Nと同一）"/>
       <sheetName val="⑥フューエル"/>
-      <sheetName val="電子ﾎﾞﾘｭｰﾑ設定値（740Nと同一）"/>
       <sheetName val="ﾌﾟﾙﾀﾞｳﾝﾒﾆｭｰ"/>
       <sheetName val="設品表01-3-23作成"/>
       <sheetName val="wire"/>
@@ -18218,25 +18423,24 @@
       <sheetName val="610L611L品番一覧"/>
       <sheetName val="【Input】見積基礎情報（海外生産分)"/>
       <sheetName val="IM-P-L-JB "/>
-      <sheetName val="797T輸入部品リスト"/>
-      <sheetName val="テーブル"/>
-      <sheetName val="Master Updated(517)"/>
-      <sheetName val="４-２．151項目累積（日本）"/>
-      <sheetName val="５-２．151項目累積（北米）"/>
-      <sheetName val="５-１．151項目詳細（北米）"/>
-      <sheetName val="545N仕様ﾗﾌ2"/>
-      <sheetName val="商品力向上"/>
-      <sheetName val="OP-PD"/>
-      <sheetName val="６２３Ｔ"/>
+      <sheetName val="RMBSS's Triggered"/>
+      <sheetName val="_"/>
       <sheetName val="Main 2"/>
       <sheetName val="Datasheet from R. Hinds"/>
-      <sheetName val="GMT900 IPC"/>
+      <sheetName val="545N仕様ﾗﾌ2"/>
+      <sheetName val="Master Updated(517)"/>
+      <sheetName val="６２３Ｔ"/>
+      <sheetName val="商品力向上"/>
+      <sheetName val="ED AND EDOV"/>
       <sheetName val="HORAS_TRAB"/>
       <sheetName val="Resumo_Corolla"/>
       <sheetName val="GASTOS_COROLLA"/>
-      <sheetName val="CALC"/>
-      <sheetName val="ﾘｽﾄ候補"/>
-      <sheetName val="ｺｰﾄﾞ表"/>
+      <sheetName val="④要素記号一覧表"/>
+      <sheetName val="START"/>
+      <sheetName val="Blue Flag"/>
+      <sheetName val="Calc Sheet Budget"/>
+      <sheetName val="見積一覧（１案）"/>
+      <sheetName val="部品"/>
       <sheetName val="①評価項目_メーカー"/>
       <sheetName val="車両仕様_x005f_x0000_4__x005f_x0000__x005f_x0011__x00"/>
       <sheetName val="車両仕様4__x005f_x0000__x005f_x0011__x005f_x0000_"/>
@@ -18263,16 +18467,9 @@
       <sheetName val="車両仕様_4___x005f_x005f_x005f_x005f_x005f_x005f_x001"/>
       <sheetName val="車両仕様4___x005f_x005f_x005f_x005f_x005f_x005f_x0011"/>
       <sheetName val="EFFY_MAZDA"/>
-      <sheetName val="ﾌﾟﾙﾀﾞｳﾝﾒﾆｭｰ用ｺｰﾄﾞ表"/>
-      <sheetName val="_"/>
-      <sheetName val="RMBSS's Triggered"/>
-      <sheetName val="ED AND EDOV"/>
-      <sheetName val="④要素記号一覧表"/>
-      <sheetName val="START"/>
-      <sheetName val="Blue Flag"/>
-      <sheetName val="Calc Sheet Budget"/>
-      <sheetName val="見積一覧（１案）"/>
-      <sheetName val="部品"/>
+      <sheetName val="４-２．151項目累積（日本）"/>
+      <sheetName val="５-２．151項目累積（北米）"/>
+      <sheetName val="５-１．151項目詳細（北米）"/>
       <sheetName val="sebelumCR"/>
       <sheetName val="08TMME"/>
       <sheetName val="VCPT"/>
@@ -18282,6 +18479,14 @@
       <sheetName val="WIP Cal Sheet"/>
       <sheetName val="Pricing overview"/>
       <sheetName val="駆動系1"/>
+      <sheetName val="797T輸入部品リスト"/>
+      <sheetName val="テーブル"/>
+      <sheetName val="OP-PD"/>
+      <sheetName val="GMT900 IPC"/>
+      <sheetName val="CALC"/>
+      <sheetName val="ﾘｽﾄ候補"/>
+      <sheetName val="ｺｰﾄﾞ表"/>
+      <sheetName val="ﾌﾟﾙﾀﾞｳﾝﾒﾆｭｰ用ｺｰﾄﾞ表"/>
       <sheetName val="393.N"/>
       <sheetName val="CæÊ _x0015_ Op"/>
       <sheetName val="ƒƒCƒ“‰æ–Ê _x0015_ Op"/>
@@ -18301,6 +18506,10 @@
       <sheetName val="車両仕様_ᵣ逰ᵣ邀ᵣ郰ᵣ"/>
       <sheetName val="他"/>
       <sheetName val="part"/>
+      <sheetName val="415T原"/>
+      <sheetName val="PAC14"/>
+      <sheetName val="部品表"/>
+      <sheetName val="■07中期明細雛形"/>
       <sheetName val="Vectra"/>
       <sheetName val="PRADO"/>
       <sheetName val="Previous"/>
@@ -18340,10 +18549,6 @@
       <sheetName val="OTHERS x620"/>
       <sheetName val="Ref"/>
       <sheetName val="TOTAL P2"/>
-      <sheetName val="415T原"/>
-      <sheetName val="PAC14"/>
-      <sheetName val="部品表"/>
-      <sheetName val="■07中期明細雛形"/>
       <sheetName val="BUYERS"/>
       <sheetName val="Status"/>
       <sheetName val="PR"/>
@@ -19331,18 +19536,18 @@
       <sheetName val="SUM"/>
       <sheetName val="ﾄﾗｯｸ"/>
       <sheetName val="00"/>
+      <sheetName val="追加検討（調光外部出力）"/>
+      <sheetName val="vocabulary"/>
+      <sheetName val="Calibration"/>
+      <sheetName val="CVBS"/>
+      <sheetName val="RGB"/>
+      <sheetName val="option"/>
       <sheetName val="課題管理"/>
       <sheetName val="C-55227AB"/>
       <sheetName val="Data Definition"/>
       <sheetName val="FC_まとめる"/>
-      <sheetName val="vocabulary"/>
-      <sheetName val="Calibration"/>
-      <sheetName val="CVBS"/>
-      <sheetName val="RGB"/>
       <sheetName val="車両仕様_4___x0011__x00"/>
       <sheetName val="ドメインリスト"/>
-      <sheetName val="option"/>
-      <sheetName val="追加検討（調光外部出力）"/>
       <sheetName val="入力規則"/>
       <sheetName val="Inf"/>
       <sheetName val="#REF!"/>
@@ -19433,8 +19638,29 @@
       <sheetName val="入力LIST"/>
       <sheetName val="パラメータ一覧(AXSS.AXCS)"/>
       <sheetName val="設定値定義"/>
+      <sheetName val="リストデータ"/>
+      <sheetName val="All"/>
+      <sheetName val="58831-06360"/>
+      <sheetName val="1999.4"/>
+      <sheetName val="車両仕様 _x005f_x0000__x005f_x0000__x005f_x000a__x000"/>
+      <sheetName val="車両仕様_x005f_x0000_ῃ_x005f_x0000__x005f_x0014__x000"/>
+      <sheetName val="車両仕様_x005f_x0000__x005f_x0000__x005f_x0000__x0000"/>
+      <sheetName val="車両仕様_x005f_x0000_ῆ玐ῆꆠῨ"/>
+      <sheetName val="車両仕様4?_x005f_x0000__x005f_x0000__x005f_x0000_"/>
+      <sheetName val="SHEET  car no"/>
       <sheetName val="車両仕様????帅?"/>
       <sheetName val="Net Price Position _ Sheet 1"/>
+      <sheetName val="Packing_List2"/>
+      <sheetName val="Packing_List"/>
+      <sheetName val="Calculation_PS"/>
+      <sheetName val="Customer_behaver"/>
+      <sheetName val="Seat_Assy_Tool_Tracking"/>
+      <sheetName val="Stock_in_Trade1"/>
+      <sheetName val="Packing_List21"/>
+      <sheetName val="Packing_List1"/>
+      <sheetName val="Calculation_PS1"/>
+      <sheetName val="Customer_behaver1"/>
+      <sheetName val="Seat_Assy_Tool_Tracking1"/>
       <sheetName val="POs"/>
       <sheetName val="計算式"/>
       <sheetName val="工管合計"/>
@@ -20958,15 +21184,9 @@
       <sheetName val="5"/>
       <sheetName val="確認ｼｰﾄ(TBU)"/>
       <sheetName val="Sheet1 (2)"/>
-      <sheetName val="SHEET  car no"/>
       <sheetName val="サイクル"/>
       <sheetName val="特殊サイクル一覧"/>
       <sheetName val="カメラ"/>
-      <sheetName val="車両仕様 _x005f_x0000__x005f_x0000__x005f_x000a__x000"/>
-      <sheetName val="車両仕様_x005f_x0000_ῃ_x005f_x0000__x005f_x0014__x000"/>
-      <sheetName val="車両仕様_x005f_x0000__x005f_x0000__x005f_x0000__x0000"/>
-      <sheetName val="車両仕様_x005f_x0000_ῆ玐ῆꆠῨ"/>
-      <sheetName val="車両仕様4?_x005f_x0000__x005f_x0000__x005f_x0000_"/>
       <sheetName val="台数"/>
       <sheetName val="MET397D-25"/>
       <sheetName val="集計表"/>
@@ -20975,21 +21195,6 @@
       <sheetName val="Ｓｉ問連"/>
       <sheetName val="アップロード系(2)"/>
       <sheetName val="エンジン型式"/>
-      <sheetName val="リストデータ"/>
-      <sheetName val="All"/>
-      <sheetName val="58831-06360"/>
-      <sheetName val="1999.4"/>
-      <sheetName val="Packing_List2"/>
-      <sheetName val="Packing_List"/>
-      <sheetName val="Calculation_PS"/>
-      <sheetName val="Customer_behaver"/>
-      <sheetName val="Seat_Assy_Tool_Tracking"/>
-      <sheetName val="Stock_in_Trade1"/>
-      <sheetName val="Packing_List21"/>
-      <sheetName val="Packing_List1"/>
-      <sheetName val="Calculation_PS1"/>
-      <sheetName val="Customer_behaver1"/>
-      <sheetName val="Seat_Assy_Tool_Tracking1"/>
       <sheetName val="Index"/>
       <sheetName val="Defined Layout Screen_Ver.0.6"/>
       <sheetName val="９ｘ"/>
@@ -21001,6 +21206,185 @@
       <sheetName val="config"/>
       <sheetName val="地点情報データ応答"/>
       <sheetName val="Par"/>
+      <sheetName val="Calcul"/>
+      <sheetName val="ETC機能判定"/>
+      <sheetName val="ETCメニュー"/>
+      <sheetName val="登録情報表示"/>
+      <sheetName val="ETC設定"/>
+      <sheetName val="履歴情報表示"/>
+      <sheetName val="履歴情報詳細表示"/>
+      <sheetName val="メニュー２"/>
+      <sheetName val="割込み(Disp)"/>
+      <sheetName val="割込み(Navi)"/>
+      <sheetName val="走行強制状態変化"/>
+      <sheetName val="入力パラメータ"/>
+      <sheetName val="DetailSequence"/>
+      <sheetName val="InterFace"/>
+      <sheetName val="FBtbl"/>
+      <sheetName val="リスト画面"/>
+      <sheetName val="特殊画面"/>
+      <sheetName val="入力画面"/>
+      <sheetName val="メッセージ受信開始"/>
+      <sheetName val="Mark"/>
+      <sheetName val="Contents"/>
+      <sheetName val="車両仕様4_ "/>
+      <sheetName val="改正履歴"/>
+      <sheetName val="リスト選択用"/>
+      <sheetName val="变更履历"/>
+      <sheetName val="Menu List"/>
+      <sheetName val="ドメイン一覧"/>
+      <sheetName val="検査シート"/>
+      <sheetName val="Cover"/>
+      <sheetName val="MIS REPORT "/>
+      <sheetName val="（別紙5-1）PP02簡素化"/>
+      <sheetName val="universal"/>
+      <sheetName val="Cost Casting"/>
+      <sheetName val="paint mtrl"/>
+      <sheetName val="corolla_095W_"/>
+      <sheetName val="dyna"/>
+      <sheetName val="FC"/>
+      <sheetName val="★ONS_MSG_list"/>
+      <sheetName val="ﾕｰｻﾞｰ設定"/>
+      <sheetName val="同行评审"/>
+      <sheetName val="5.心配点抽出-0"/>
+      <sheetName val="0.表紙"/>
+      <sheetName val="1._概要"/>
+      <sheetName val="4 選局"/>
+      <sheetName val="定数"/>
+      <sheetName val="Case 21_1"/>
+      <sheetName val="96期(川崎)"/>
+      <sheetName val="ORDSHP"/>
+      <sheetName val="B"/>
+      <sheetName val="Blue_Flag3"/>
+      <sheetName val="Calc_Sheet_Budget3"/>
+      <sheetName val="_PART_479W_LHD3"/>
+      <sheetName val="_PART_MYY5A3"/>
+      <sheetName val="393_N3"/>
+      <sheetName val="WIP_Cal_Sheet3"/>
+      <sheetName val="Pricing_overview3"/>
+      <sheetName val="Lookup_Table3"/>
+      <sheetName val="promo_lists_20113"/>
+      <sheetName val="車両仕様_嗼1嗼1噌1鲌3"/>
+      <sheetName val="車両仕様_勜+勜+匬+鲌3"/>
+      <sheetName val="EquipmentTrimming_Cabin_NS3"/>
+      <sheetName val="Reference_3"/>
+      <sheetName val="車両仕様__x005f_x0000__x005f_x0000_?_x005f_x0012_?瞳?3"/>
+      <sheetName val="車両仕様_???_x005f_x0012_?瞳?3"/>
+      <sheetName val="160th_NPCC_Nov'103"/>
+      <sheetName val="RMBSS's_Triggered3"/>
+      <sheetName val="車両仕様?4???_??3"/>
+      <sheetName val="車両仕様_???_?瞳?3"/>
+      <sheetName val="車両仕様???ꎨ_窉瞳㾐3"/>
+      <sheetName val="車両仕様?4??_?3"/>
+      <sheetName val="車両仕様4??_?3"/>
+      <sheetName val="車両仕様____瞳_3"/>
+      <sheetName val="車両仕様______瞳_3"/>
+      <sheetName val="車両仕様_4______3"/>
+      <sheetName val="車両仕様___ꎨ_窉瞳㾐3"/>
+      <sheetName val="車両仕様_4____3"/>
+      <sheetName val="車両仕様4____3"/>
+      <sheetName val="PRICE_LIST3"/>
+      <sheetName val="Loss_Time3"/>
+      <sheetName val="Price_range_IT3"/>
+      <sheetName val="Avensis+d_seg__in_&amp;_out_of_UK+3"/>
+      <sheetName val="#ofclose__xl3"/>
+      <sheetName val="Annexes_toutes_bases3"/>
+      <sheetName val="DON_GIA3"/>
+      <sheetName val="CHITIET_VL-NC3"/>
+      <sheetName val="TONGKE3p_3"/>
+      <sheetName val="TOTAL_P23"/>
+      <sheetName val="2_-_Summary3"/>
+      <sheetName val="IPOTESI_PIANO_STATICA3"/>
+      <sheetName val="make_up3"/>
+      <sheetName val="車両仕様_???_x005f_x005f_x005f_x0012_?瞳?3"/>
+      <sheetName val="調達担当者(06_2～)3"/>
+      <sheetName val="車両仕様__x005f_x0000__2"/>
+      <sheetName val="車両仕様_x005f_x0000__N2"/>
+      <sheetName val="車両仕様___x005f_x0012_2"/>
+      <sheetName val="車両仕様__x005f_x005f_x2"/>
+      <sheetName val="車両仕様___x005f_x005f_2"/>
+      <sheetName val="05-065_she2"/>
+      <sheetName val="idgr_-_formula2"/>
+      <sheetName val="IDGR_(3)2"/>
+      <sheetName val="IDGR_(2)2"/>
+      <sheetName val="PLIV_(3)2"/>
+      <sheetName val="PLIV_(2)2"/>
+      <sheetName val="PLIV_(template)2"/>
+      <sheetName val="inv_recon2"/>
+      <sheetName val="side_member2"/>
+      <sheetName val="TTC_(FG)2"/>
+      <sheetName val="Sheet1_(3)2"/>
+      <sheetName val="truck_allocation2"/>
+      <sheetName val="Supplier_Price_Check2"/>
+      <sheetName val="$_-_june2"/>
+      <sheetName val="Vios_Cost_Reduction_actual_pro2"/>
+      <sheetName val="RET_PALLET2"/>
+      <sheetName val="Form_A2"/>
+      <sheetName val="NG_SUMMARY2"/>
+      <sheetName val="impact_pallet_and_racks2"/>
+      <sheetName val="Daily_WSD2"/>
+      <sheetName val="ass'y_12'04-05'053"/>
+      <sheetName val="Type_I2"/>
+      <sheetName val="Schedule_PM2"/>
+      <sheetName val="training_forklift2"/>
+      <sheetName val="Budget_by_Category2"/>
+      <sheetName val="investment_tmc_v8_0_34p2"/>
+      <sheetName val="PTD_Activity2"/>
+      <sheetName val="Sample_1PP_2"/>
+      <sheetName val="Open_Ran3"/>
+      <sheetName val="Open_RAN_23"/>
+      <sheetName val="CHIA_KH2"/>
+      <sheetName val="Purch__BP2"/>
+      <sheetName val="車両仕様_____x005f_x005f_x005f_x005f_x0013"/>
+      <sheetName val="車両仕様_____x005f_x005f_x005f_x005f_x0053"/>
+      <sheetName val="ＰＲＥ_NO1"/>
+      <sheetName val="Courier_4x2"/>
+      <sheetName val="Price_Trend2"/>
+      <sheetName val="車両仕様_?_x005f_x0012_?瞳?2"/>
+      <sheetName val="YARIS_HB2"/>
+      <sheetName val="00_KS"/>
+      <sheetName val="PRADO_3Dr_fl2"/>
+      <sheetName val="01_DATA2"/>
+      <sheetName val="Quality_Update2"/>
+      <sheetName val="prior_data"/>
+      <sheetName val="Table_Master"/>
+      <sheetName val="1_概述"/>
+      <sheetName val="Drop-down_Menu_List"/>
+      <sheetName val="Open_Item_List"/>
+      <sheetName val="本修正_DIFF_"/>
+      <sheetName val="Sector_Assignment"/>
+      <sheetName val="BQ_CONVEYOR"/>
+      <sheetName val="IMV_LIST_2003"/>
+      <sheetName val="車両仕様_x005f_x0000_4__x005f_x0000__x005f_x0000___x0"/>
+      <sheetName val="車両仕様__x005f_x0000__x005f_x0000____瞳_"/>
+      <sheetName val="Part_list"/>
+      <sheetName val="INACT797"/>
+      <sheetName val="M1A"/>
+      <sheetName val="OK"/>
+      <sheetName val="??? Pilling upu_S y"/>
+      <sheetName val="ASF INVENTORY"/>
+      <sheetName val="車両仕様_4___x005f_x0013__x0013__x0013__x0013__x0013_"/>
+      <sheetName val="ጀጀ؀ԀЀࠀ᐀Ѐऀ܀̀܀ഀ܀Ԁऀ଀ࠀ_x0000_"/>
+      <sheetName val="CTable"/>
+      <sheetName val="bs is"/>
+      <sheetName val="成績"/>
+      <sheetName val="IT Checklist"/>
+      <sheetName val="ﾊﾟｲﾌﾟ"/>
+      <sheetName val="冷延鋼板"/>
+      <sheetName val="熱延鋼板"/>
+      <sheetName val="他材料費"/>
+      <sheetName val="No.31"/>
+      <sheetName val="コマンド認識, DTMF"/>
+      <sheetName val="CS2_SmcDriverインテグ項目"/>
+      <sheetName val="標準仕様DB"/>
+      <sheetName val="BEEP設定"/>
+      <sheetName val="休日"/>
+      <sheetName val="工数ｺｰﾄﾞﾘｽﾄ"/>
+      <sheetName val="5．キー入力動作説明"/>
+      <sheetName val="日程"/>
+      <sheetName val="進捗"/>
+      <sheetName val="印刷"/>
+      <sheetName val="試験項目_R3小"/>
     </sheetNames>
     <sheetDataSet>
       <sheetData sheetId="0" refreshError="1"/>
@@ -21556,33 +21940,45 @@
       <sheetData sheetId="304" refreshError="1"/>
       <sheetData sheetId="305" refreshError="1"/>
       <sheetData sheetId="306" refreshError="1"/>
-      <sheetData sheetId="307">
+      <sheetData sheetId="307" refreshError="1"/>
+      <sheetData sheetId="308" refreshError="1"/>
+      <sheetData sheetId="309" refreshError="1"/>
+      <sheetData sheetId="310" refreshError="1"/>
+      <sheetData sheetId="311">
         <row r="1">
           <cell r="B1" t="str">
             <v>1</v>
           </cell>
         </row>
       </sheetData>
-      <sheetData sheetId="308">
+      <sheetData sheetId="312">
         <row r="1">
           <cell r="B1" t="str">
             <v>1</v>
           </cell>
         </row>
       </sheetData>
-      <sheetData sheetId="309">
+      <sheetData sheetId="313">
         <row r="1">
           <cell r="B1" t="str">
             <v>1</v>
           </cell>
         </row>
       </sheetData>
-      <sheetData sheetId="310"/>
-      <sheetData sheetId="311"/>
-      <sheetData sheetId="312" refreshError="1"/>
-      <sheetData sheetId="313" refreshError="1"/>
-      <sheetData sheetId="314" refreshError="1"/>
-      <sheetData sheetId="315" refreshError="1"/>
+      <sheetData sheetId="314">
+        <row r="1">
+          <cell r="B1" t="str">
+            <v>1</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="315">
+        <row r="1">
+          <cell r="B1" t="str">
+            <v>1</v>
+          </cell>
+        </row>
+      </sheetData>
       <sheetData sheetId="316" refreshError="1"/>
       <sheetData sheetId="317" refreshError="1"/>
       <sheetData sheetId="318" refreshError="1"/>
@@ -23154,8 +23550,8 @@
       </sheetData>
       <sheetData sheetId="793">
         <row r="1">
-          <cell r="B1" t="str">
-            <v>1</v>
+          <cell r="A1" t="str">
+            <v>ﾄﾖﾀ自動車株式会社　調達本部　</v>
           </cell>
         </row>
       </sheetData>
@@ -23191,7 +23587,13 @@
       <sheetData sheetId="805" refreshError="1"/>
       <sheetData sheetId="806" refreshError="1"/>
       <sheetData sheetId="807" refreshError="1"/>
-      <sheetData sheetId="808"/>
+      <sheetData sheetId="808">
+        <row r="3">
+          <cell r="B3" t="str">
+            <v>TOYOTA   TSUSHO  PHILIPPINES CORPORATION</v>
+          </cell>
+        </row>
+      </sheetData>
       <sheetData sheetId="809" refreshError="1"/>
       <sheetData sheetId="810" refreshError="1"/>
       <sheetData sheetId="811" refreshError="1"/>
@@ -24154,9 +24556,9 @@
         </row>
       </sheetData>
       <sheetData sheetId="1050">
-        <row r="3">
-          <cell r="B3" t="str">
-            <v>TOYOTA   TSUSHO  PHILIPPINES CORPORATION</v>
+        <row r="1">
+          <cell r="B1" t="str">
+            <v>1</v>
           </cell>
         </row>
       </sheetData>
@@ -24378,9 +24780,9 @@
         </row>
       </sheetData>
       <sheetData sheetId="1082">
-        <row r="3">
-          <cell r="B3" t="str">
-            <v>TOYOTA   TSUSHO  PHILIPPINES CORPORATION</v>
+        <row r="1">
+          <cell r="B1" t="str">
+            <v>1</v>
           </cell>
         </row>
       </sheetData>
@@ -24399,9 +24801,9 @@
         </row>
       </sheetData>
       <sheetData sheetId="1085">
-        <row r="3">
-          <cell r="B3" t="str">
-            <v>TOYOTA   TSUSHO  PHILIPPINES CORPORATION</v>
+        <row r="1">
+          <cell r="B1" t="str">
+            <v>1</v>
           </cell>
         </row>
       </sheetData>
@@ -24728,9 +25130,9 @@
         </row>
       </sheetData>
       <sheetData sheetId="1132">
-        <row r="3">
-          <cell r="B3" t="str">
-            <v>TOYOTA   TSUSHO  PHILIPPINES CORPORATION</v>
+        <row r="1">
+          <cell r="B1" t="str">
+            <v>1</v>
           </cell>
         </row>
       </sheetData>
@@ -24819,9 +25221,9 @@
         </row>
       </sheetData>
       <sheetData sheetId="1145">
-        <row r="3">
-          <cell r="B3" t="str">
-            <v>TOYOTA   TSUSHO  PHILIPPINES CORPORATION</v>
+        <row r="1">
+          <cell r="B1" t="str">
+            <v>1</v>
           </cell>
         </row>
       </sheetData>
@@ -25050,16 +25452,16 @@
         </row>
       </sheetData>
       <sheetData sheetId="1178">
-        <row r="3">
-          <cell r="B3" t="str">
-            <v>TOYOTA   TSUSHO  PHILIPPINES CORPORATION</v>
+        <row r="1">
+          <cell r="B1" t="str">
+            <v>1</v>
           </cell>
         </row>
       </sheetData>
       <sheetData sheetId="1179">
-        <row r="3">
-          <cell r="B3" t="str">
-            <v>TOYOTA   TSUSHO  PHILIPPINES CORPORATION</v>
+        <row r="1">
+          <cell r="B1" t="str">
+            <v>1</v>
           </cell>
         </row>
       </sheetData>
@@ -25099,9 +25501,9 @@
         </row>
       </sheetData>
       <sheetData sheetId="1185">
-        <row r="3">
-          <cell r="B3" t="str">
-            <v>TOYOTA   TSUSHO  PHILIPPINES CORPORATION</v>
+        <row r="1">
+          <cell r="B1" t="str">
+            <v>1</v>
           </cell>
         </row>
       </sheetData>
@@ -25127,9 +25529,9 @@
         </row>
       </sheetData>
       <sheetData sheetId="1189">
-        <row r="3">
-          <cell r="B3" t="str">
-            <v>TOYOTA   TSUSHO  PHILIPPINES CORPORATION</v>
+        <row r="1">
+          <cell r="B1" t="str">
+            <v>1</v>
           </cell>
         </row>
       </sheetData>
@@ -25148,9 +25550,9 @@
         </row>
       </sheetData>
       <sheetData sheetId="1192">
-        <row r="3">
-          <cell r="B3" t="str">
-            <v>TOYOTA   TSUSHO  PHILIPPINES CORPORATION</v>
+        <row r="1">
+          <cell r="B1" t="str">
+            <v>1</v>
           </cell>
         </row>
       </sheetData>
@@ -25218,9 +25620,9 @@
         </row>
       </sheetData>
       <sheetData sheetId="1202">
-        <row r="3">
-          <cell r="B3" t="str">
-            <v>TOYOTA   TSUSHO  PHILIPPINES CORPORATION</v>
+        <row r="1">
+          <cell r="B1" t="str">
+            <v>1</v>
           </cell>
         </row>
       </sheetData>
@@ -25239,16 +25641,16 @@
         </row>
       </sheetData>
       <sheetData sheetId="1205">
-        <row r="3">
-          <cell r="B3" t="str">
-            <v>TOYOTA   TSUSHO  PHILIPPINES CORPORATION</v>
+        <row r="1">
+          <cell r="B1" t="str">
+            <v>1</v>
           </cell>
         </row>
       </sheetData>
       <sheetData sheetId="1206">
-        <row r="3">
-          <cell r="B3" t="str">
-            <v>TOYOTA   TSUSHO  PHILIPPINES CORPORATION</v>
+        <row r="1">
+          <cell r="B1" t="str">
+            <v>1</v>
           </cell>
         </row>
       </sheetData>
@@ -25260,16 +25662,16 @@
         </row>
       </sheetData>
       <sheetData sheetId="1208">
-        <row r="3">
-          <cell r="B3" t="str">
-            <v>TOYOTA   TSUSHO  PHILIPPINES CORPORATION</v>
+        <row r="1">
+          <cell r="B1" t="str">
+            <v>1</v>
           </cell>
         </row>
       </sheetData>
       <sheetData sheetId="1209">
-        <row r="3">
-          <cell r="B3" t="str">
-            <v>TOYOTA   TSUSHO  PHILIPPINES CORPORATION</v>
+        <row r="1">
+          <cell r="B1" t="str">
+            <v>1</v>
           </cell>
         </row>
       </sheetData>
@@ -25309,9 +25711,9 @@
         </row>
       </sheetData>
       <sheetData sheetId="1215">
-        <row r="3">
-          <cell r="B3" t="str">
-            <v>TOYOTA   TSUSHO  PHILIPPINES CORPORATION</v>
+        <row r="1">
+          <cell r="B1" t="str">
+            <v>1</v>
           </cell>
         </row>
       </sheetData>
@@ -25337,9 +25739,9 @@
         </row>
       </sheetData>
       <sheetData sheetId="1219">
-        <row r="3">
-          <cell r="B3" t="str">
-            <v>TOYOTA   TSUSHO  PHILIPPINES CORPORATION</v>
+        <row r="1">
+          <cell r="B1" t="str">
+            <v>1</v>
           </cell>
         </row>
       </sheetData>
@@ -25358,9 +25760,9 @@
         </row>
       </sheetData>
       <sheetData sheetId="1222">
-        <row r="3">
-          <cell r="B3" t="str">
-            <v>TOYOTA   TSUSHO  PHILIPPINES CORPORATION</v>
+        <row r="1">
+          <cell r="B1" t="str">
+            <v>1</v>
           </cell>
         </row>
       </sheetData>
@@ -25428,9 +25830,9 @@
         </row>
       </sheetData>
       <sheetData sheetId="1232">
-        <row r="3">
-          <cell r="B3" t="str">
-            <v>TOYOTA   TSUSHO  PHILIPPINES CORPORATION</v>
+        <row r="1">
+          <cell r="B1" t="str">
+            <v>1</v>
           </cell>
         </row>
       </sheetData>
@@ -25449,16 +25851,16 @@
         </row>
       </sheetData>
       <sheetData sheetId="1235">
-        <row r="3">
-          <cell r="B3" t="str">
-            <v>TOYOTA   TSUSHO  PHILIPPINES CORPORATION</v>
+        <row r="1">
+          <cell r="B1" t="str">
+            <v>1</v>
           </cell>
         </row>
       </sheetData>
       <sheetData sheetId="1236">
-        <row r="3">
-          <cell r="B3" t="str">
-            <v>TOYOTA   TSUSHO  PHILIPPINES CORPORATION</v>
+        <row r="1">
+          <cell r="B1" t="str">
+            <v>1</v>
           </cell>
         </row>
       </sheetData>
@@ -25470,16 +25872,16 @@
         </row>
       </sheetData>
       <sheetData sheetId="1238">
-        <row r="3">
-          <cell r="B3" t="str">
-            <v>TOYOTA   TSUSHO  PHILIPPINES CORPORATION</v>
+        <row r="1">
+          <cell r="B1" t="str">
+            <v>1</v>
           </cell>
         </row>
       </sheetData>
       <sheetData sheetId="1239">
-        <row r="3">
-          <cell r="B3" t="str">
-            <v>TOYOTA   TSUSHO  PHILIPPINES CORPORATION</v>
+        <row r="1">
+          <cell r="B1" t="str">
+            <v>1</v>
           </cell>
         </row>
       </sheetData>
@@ -25519,16 +25921,16 @@
         </row>
       </sheetData>
       <sheetData sheetId="1245">
-        <row r="3">
-          <cell r="B3" t="str">
-            <v>TOYOTA   TSUSHO  PHILIPPINES CORPORATION</v>
+        <row r="1">
+          <cell r="B1" t="str">
+            <v>1</v>
           </cell>
         </row>
       </sheetData>
       <sheetData sheetId="1246">
-        <row r="3">
-          <cell r="B3" t="str">
-            <v>TOYOTA   TSUSHO  PHILIPPINES CORPORATION</v>
+        <row r="1">
+          <cell r="B1" t="str">
+            <v>1</v>
           </cell>
         </row>
       </sheetData>
@@ -25588,16 +25990,76 @@
       <sheetData sheetId="1294"/>
       <sheetData sheetId="1295" refreshError="1"/>
       <sheetData sheetId="1296" refreshError="1"/>
-      <sheetData sheetId="1297"/>
-      <sheetData sheetId="1298"/>
-      <sheetData sheetId="1299"/>
-      <sheetData sheetId="1300"/>
-      <sheetData sheetId="1301"/>
-      <sheetData sheetId="1302"/>
-      <sheetData sheetId="1303"/>
-      <sheetData sheetId="1304"/>
-      <sheetData sheetId="1305"/>
-      <sheetData sheetId="1306"/>
+      <sheetData sheetId="1297">
+        <row r="1">
+          <cell r="B1" t="str">
+            <v>1</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="1298">
+        <row r="1">
+          <cell r="B1" t="str">
+            <v>1</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="1299">
+        <row r="1">
+          <cell r="B1" t="str">
+            <v>1</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="1300">
+        <row r="1">
+          <cell r="B1" t="str">
+            <v>1</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="1301">
+        <row r="1">
+          <cell r="B1" t="str">
+            <v>1</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="1302">
+        <row r="1">
+          <cell r="B1" t="str">
+            <v>1</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="1303">
+        <row r="1">
+          <cell r="B1" t="str">
+            <v>1</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="1304">
+        <row r="1">
+          <cell r="B1" t="str">
+            <v>1</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="1305">
+        <row r="1">
+          <cell r="B1" t="str">
+            <v>1</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="1306">
+        <row r="1">
+          <cell r="B1" t="str">
+            <v>1</v>
+          </cell>
+        </row>
+      </sheetData>
       <sheetData sheetId="1307" refreshError="1"/>
       <sheetData sheetId="1308" refreshError="1"/>
       <sheetData sheetId="1309" refreshError="1"/>
@@ -25607,13 +26069,13 @@
       <sheetData sheetId="1313" refreshError="1"/>
       <sheetData sheetId="1314" refreshError="1"/>
       <sheetData sheetId="1315" refreshError="1"/>
-      <sheetData sheetId="1316"/>
+      <sheetData sheetId="1316" refreshError="1"/>
       <sheetData sheetId="1317" refreshError="1"/>
       <sheetData sheetId="1318" refreshError="1"/>
       <sheetData sheetId="1319" refreshError="1"/>
       <sheetData sheetId="1320" refreshError="1"/>
       <sheetData sheetId="1321" refreshError="1"/>
-      <sheetData sheetId="1322" refreshError="1"/>
+      <sheetData sheetId="1322"/>
       <sheetData sheetId="1323" refreshError="1"/>
       <sheetData sheetId="1324" refreshError="1"/>
       <sheetData sheetId="1325" refreshError="1"/>
@@ -25708,39 +26170,33 @@
       <sheetData sheetId="1414" refreshError="1"/>
       <sheetData sheetId="1415" refreshError="1"/>
       <sheetData sheetId="1416" refreshError="1"/>
-      <sheetData sheetId="1417"/>
+      <sheetData sheetId="1417" refreshError="1"/>
       <sheetData sheetId="1418" refreshError="1"/>
       <sheetData sheetId="1419" refreshError="1"/>
       <sheetData sheetId="1420" refreshError="1"/>
       <sheetData sheetId="1421" refreshError="1"/>
       <sheetData sheetId="1422" refreshError="1"/>
-      <sheetData sheetId="1423"/>
-      <sheetData sheetId="1424"/>
-      <sheetData sheetId="1425"/>
-      <sheetData sheetId="1426"/>
+      <sheetData sheetId="1423" refreshError="1"/>
+      <sheetData sheetId="1424" refreshError="1"/>
+      <sheetData sheetId="1425" refreshError="1"/>
+      <sheetData sheetId="1426" refreshError="1"/>
       <sheetData sheetId="1427"/>
-      <sheetData sheetId="1428"/>
+      <sheetData sheetId="1428" refreshError="1"/>
       <sheetData sheetId="1429"/>
       <sheetData sheetId="1430"/>
       <sheetData sheetId="1431"/>
       <sheetData sheetId="1432"/>
       <sheetData sheetId="1433"/>
-      <sheetData sheetId="1434" refreshError="1"/>
-      <sheetData sheetId="1435">
-        <row r="3">
-          <cell r="C3" t="str">
-            <v>2022年</v>
-          </cell>
-        </row>
-      </sheetData>
+      <sheetData sheetId="1434"/>
+      <sheetData sheetId="1435"/>
       <sheetData sheetId="1436"/>
       <sheetData sheetId="1437"/>
       <sheetData sheetId="1438"/>
       <sheetData sheetId="1439"/>
-      <sheetData sheetId="1440"/>
-      <sheetData sheetId="1441"/>
-      <sheetData sheetId="1442"/>
-      <sheetData sheetId="1443"/>
+      <sheetData sheetId="1440" refreshError="1"/>
+      <sheetData sheetId="1441" refreshError="1"/>
+      <sheetData sheetId="1442" refreshError="1"/>
+      <sheetData sheetId="1443" refreshError="1"/>
       <sheetData sheetId="1444"/>
       <sheetData sheetId="1445"/>
       <sheetData sheetId="1446"/>
@@ -25752,8 +26208,14 @@
       <sheetData sheetId="1452"/>
       <sheetData sheetId="1453"/>
       <sheetData sheetId="1454"/>
-      <sheetData sheetId="1455"/>
-      <sheetData sheetId="1456"/>
+      <sheetData sheetId="1455" refreshError="1"/>
+      <sheetData sheetId="1456">
+        <row r="3">
+          <cell r="C3" t="str">
+            <v>2022年</v>
+          </cell>
+        </row>
+      </sheetData>
       <sheetData sheetId="1457"/>
       <sheetData sheetId="1458"/>
       <sheetData sheetId="1459"/>
@@ -25833,19 +26295,73 @@
       <sheetData sheetId="1533"/>
       <sheetData sheetId="1534"/>
       <sheetData sheetId="1535"/>
-      <sheetData sheetId="1536"/>
-      <sheetData sheetId="1537"/>
+      <sheetData sheetId="1536">
+        <row r="1">
+          <cell r="B1" t="str">
+            <v>1</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="1537">
+        <row r="1">
+          <cell r="B1" t="str">
+            <v>1</v>
+          </cell>
+        </row>
+      </sheetData>
       <sheetData sheetId="1538"/>
-      <sheetData sheetId="1539"/>
+      <sheetData sheetId="1539">
+        <row r="1">
+          <cell r="B1" t="str">
+            <v>1</v>
+          </cell>
+        </row>
+      </sheetData>
       <sheetData sheetId="1540"/>
-      <sheetData sheetId="1541"/>
-      <sheetData sheetId="1542"/>
-      <sheetData sheetId="1543"/>
+      <sheetData sheetId="1541">
+        <row r="1">
+          <cell r="B1" t="str">
+            <v>1</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="1542">
+        <row r="1">
+          <cell r="B1" t="str">
+            <v>1</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="1543">
+        <row r="1">
+          <cell r="B1" t="str">
+            <v>1</v>
+          </cell>
+        </row>
+      </sheetData>
       <sheetData sheetId="1544"/>
-      <sheetData sheetId="1545"/>
+      <sheetData sheetId="1545">
+        <row r="1">
+          <cell r="B1" t="str">
+            <v>1</v>
+          </cell>
+        </row>
+      </sheetData>
       <sheetData sheetId="1546"/>
-      <sheetData sheetId="1547"/>
-      <sheetData sheetId="1548"/>
+      <sheetData sheetId="1547">
+        <row r="1">
+          <cell r="B1" t="str">
+            <v>1</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="1548">
+        <row r="1">
+          <cell r="B1" t="str">
+            <v>1</v>
+          </cell>
+        </row>
+      </sheetData>
       <sheetData sheetId="1549"/>
       <sheetData sheetId="1550"/>
       <sheetData sheetId="1551"/>
@@ -27235,52 +27751,52 @@
       <sheetData sheetId="2935"/>
       <sheetData sheetId="2936"/>
       <sheetData sheetId="2937"/>
-      <sheetData sheetId="2938">
+      <sheetData sheetId="2938"/>
+      <sheetData sheetId="2939"/>
+      <sheetData sheetId="2940"/>
+      <sheetData sheetId="2941"/>
+      <sheetData sheetId="2942"/>
+      <sheetData sheetId="2943"/>
+      <sheetData sheetId="2944"/>
+      <sheetData sheetId="2945"/>
+      <sheetData sheetId="2946"/>
+      <sheetData sheetId="2947"/>
+      <sheetData sheetId="2948"/>
+      <sheetData sheetId="2949"/>
+      <sheetData sheetId="2950"/>
+      <sheetData sheetId="2951"/>
+      <sheetData sheetId="2952"/>
+      <sheetData sheetId="2953"/>
+      <sheetData sheetId="2954"/>
+      <sheetData sheetId="2955"/>
+      <sheetData sheetId="2956"/>
+      <sheetData sheetId="2957"/>
+      <sheetData sheetId="2958"/>
+      <sheetData sheetId="2959">
         <row r="1">
           <cell r="A1"/>
         </row>
       </sheetData>
-      <sheetData sheetId="2939"/>
-      <sheetData sheetId="2940"/>
-      <sheetData sheetId="2941"/>
-      <sheetData sheetId="2942" refreshError="1"/>
-      <sheetData sheetId="2943">
+      <sheetData sheetId="2960"/>
+      <sheetData sheetId="2961"/>
+      <sheetData sheetId="2962"/>
+      <sheetData sheetId="2963">
         <row r="1">
           <cell r="B1" t="str">
             <v>文章管理番号</v>
           </cell>
         </row>
       </sheetData>
-      <sheetData sheetId="2944"/>
-      <sheetData sheetId="2945" refreshError="1"/>
-      <sheetData sheetId="2946" refreshError="1"/>
-      <sheetData sheetId="2947" refreshError="1"/>
-      <sheetData sheetId="2948" refreshError="1"/>
-      <sheetData sheetId="2949" refreshError="1"/>
-      <sheetData sheetId="2950" refreshError="1"/>
-      <sheetData sheetId="2951" refreshError="1"/>
-      <sheetData sheetId="2952" refreshError="1"/>
-      <sheetData sheetId="2953" refreshError="1"/>
-      <sheetData sheetId="2954" refreshError="1"/>
-      <sheetData sheetId="2955" refreshError="1"/>
-      <sheetData sheetId="2956" refreshError="1"/>
-      <sheetData sheetId="2957" refreshError="1"/>
-      <sheetData sheetId="2958" refreshError="1"/>
-      <sheetData sheetId="2959" refreshError="1"/>
-      <sheetData sheetId="2960" refreshError="1"/>
-      <sheetData sheetId="2961" refreshError="1"/>
-      <sheetData sheetId="2962" refreshError="1"/>
-      <sheetData sheetId="2963"/>
       <sheetData sheetId="2964"/>
-      <sheetData sheetId="2965"/>
-      <sheetData sheetId="2966"/>
-      <sheetData sheetId="2967"/>
-      <sheetData sheetId="2968"/>
-      <sheetData sheetId="2969"/>
-      <sheetData sheetId="2970"/>
-      <sheetData sheetId="2971"/>
-      <sheetData sheetId="2972"/>
-      <sheetData sheetId="2973"/>
+      <sheetData sheetId="2965" refreshError="1"/>
+      <sheetData sheetId="2966" refreshError="1"/>
+      <sheetData sheetId="2967" refreshError="1"/>
+      <sheetData sheetId="2968" refreshError="1"/>
+      <sheetData sheetId="2969" refreshError="1"/>
+      <sheetData sheetId="2970" refreshError="1"/>
+      <sheetData sheetId="2971" refreshError="1"/>
+      <sheetData sheetId="2972" refreshError="1"/>
+      <sheetData sheetId="2973" refreshError="1"/>
       <sheetData sheetId="2974" refreshError="1"/>
       <sheetData sheetId="2975"/>
       <sheetData sheetId="2976" refreshError="1"/>
@@ -27292,6 +27808,323 @@
       <sheetData sheetId="2982" refreshError="1"/>
       <sheetData sheetId="2983" refreshError="1"/>
       <sheetData sheetId="2984" refreshError="1"/>
+      <sheetData sheetId="2985" refreshError="1"/>
+      <sheetData sheetId="2986" refreshError="1"/>
+      <sheetData sheetId="2987" refreshError="1"/>
+      <sheetData sheetId="2988" refreshError="1"/>
+      <sheetData sheetId="2989" refreshError="1"/>
+      <sheetData sheetId="2990" refreshError="1"/>
+      <sheetData sheetId="2991" refreshError="1"/>
+      <sheetData sheetId="2992" refreshError="1"/>
+      <sheetData sheetId="2993" refreshError="1"/>
+      <sheetData sheetId="2994" refreshError="1"/>
+      <sheetData sheetId="2995" refreshError="1"/>
+      <sheetData sheetId="2996" refreshError="1"/>
+      <sheetData sheetId="2997" refreshError="1"/>
+      <sheetData sheetId="2998" refreshError="1"/>
+      <sheetData sheetId="2999" refreshError="1"/>
+      <sheetData sheetId="3000" refreshError="1"/>
+      <sheetData sheetId="3001" refreshError="1"/>
+      <sheetData sheetId="3002" refreshError="1"/>
+      <sheetData sheetId="3003" refreshError="1"/>
+      <sheetData sheetId="3004" refreshError="1"/>
+      <sheetData sheetId="3005" refreshError="1"/>
+      <sheetData sheetId="3006" refreshError="1"/>
+      <sheetData sheetId="3007" refreshError="1"/>
+      <sheetData sheetId="3008" refreshError="1"/>
+      <sheetData sheetId="3009" refreshError="1"/>
+      <sheetData sheetId="3010" refreshError="1"/>
+      <sheetData sheetId="3011" refreshError="1"/>
+      <sheetData sheetId="3012" refreshError="1"/>
+      <sheetData sheetId="3013" refreshError="1"/>
+      <sheetData sheetId="3014" refreshError="1"/>
+      <sheetData sheetId="3015" refreshError="1"/>
+      <sheetData sheetId="3016" refreshError="1"/>
+      <sheetData sheetId="3017" refreshError="1"/>
+      <sheetData sheetId="3018" refreshError="1"/>
+      <sheetData sheetId="3019" refreshError="1"/>
+      <sheetData sheetId="3020" refreshError="1"/>
+      <sheetData sheetId="3021" refreshError="1"/>
+      <sheetData sheetId="3022" refreshError="1"/>
+      <sheetData sheetId="3023" refreshError="1"/>
+      <sheetData sheetId="3024" refreshError="1"/>
+      <sheetData sheetId="3025" refreshError="1"/>
+      <sheetData sheetId="3026" refreshError="1"/>
+      <sheetData sheetId="3027" refreshError="1"/>
+      <sheetData sheetId="3028" refreshError="1"/>
+      <sheetData sheetId="3029" refreshError="1"/>
+      <sheetData sheetId="3030" refreshError="1"/>
+      <sheetData sheetId="3031" refreshError="1"/>
+      <sheetData sheetId="3032" refreshError="1"/>
+      <sheetData sheetId="3033" refreshError="1"/>
+      <sheetData sheetId="3034"/>
+      <sheetData sheetId="3035"/>
+      <sheetData sheetId="3036"/>
+      <sheetData sheetId="3037"/>
+      <sheetData sheetId="3038"/>
+      <sheetData sheetId="3039"/>
+      <sheetData sheetId="3040"/>
+      <sheetData sheetId="3041"/>
+      <sheetData sheetId="3042"/>
+      <sheetData sheetId="3043"/>
+      <sheetData sheetId="3044"/>
+      <sheetData sheetId="3045"/>
+      <sheetData sheetId="3046"/>
+      <sheetData sheetId="3047"/>
+      <sheetData sheetId="3048"/>
+      <sheetData sheetId="3049"/>
+      <sheetData sheetId="3050"/>
+      <sheetData sheetId="3051"/>
+      <sheetData sheetId="3052"/>
+      <sheetData sheetId="3053"/>
+      <sheetData sheetId="3054"/>
+      <sheetData sheetId="3055"/>
+      <sheetData sheetId="3056"/>
+      <sheetData sheetId="3057"/>
+      <sheetData sheetId="3058"/>
+      <sheetData sheetId="3059"/>
+      <sheetData sheetId="3060"/>
+      <sheetData sheetId="3061"/>
+      <sheetData sheetId="3062"/>
+      <sheetData sheetId="3063"/>
+      <sheetData sheetId="3064"/>
+      <sheetData sheetId="3065"/>
+      <sheetData sheetId="3066"/>
+      <sheetData sheetId="3067"/>
+      <sheetData sheetId="3068"/>
+      <sheetData sheetId="3069"/>
+      <sheetData sheetId="3070"/>
+      <sheetData sheetId="3071"/>
+      <sheetData sheetId="3072"/>
+      <sheetData sheetId="3073"/>
+      <sheetData sheetId="3074"/>
+      <sheetData sheetId="3075"/>
+      <sheetData sheetId="3076"/>
+      <sheetData sheetId="3077">
+        <row r="3">
+          <cell r="B3" t="str">
+            <v>TOYOTA   TSUSHO  PHILIPPINES CORPORATION</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="3078">
+        <row r="3">
+          <cell r="B3" t="str">
+            <v>TOYOTA   TSUSHO  PHILIPPINES CORPORATION</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="3079">
+        <row r="3">
+          <cell r="B3" t="str">
+            <v>TOYOTA   TSUSHO  PHILIPPINES CORPORATION</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="3080">
+        <row r="3">
+          <cell r="B3" t="str">
+            <v>TOYOTA   TSUSHO  PHILIPPINES CORPORATION</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="3081">
+        <row r="3">
+          <cell r="B3" t="str">
+            <v>TOYOTA   TSUSHO  PHILIPPINES CORPORATION</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="3082">
+        <row r="3">
+          <cell r="B3" t="str">
+            <v>TOYOTA   TSUSHO  PHILIPPINES CORPORATION</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="3083">
+        <row r="3">
+          <cell r="B3" t="str">
+            <v>TOYOTA   TSUSHO  PHILIPPINES CORPORATION</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="3084">
+        <row r="3">
+          <cell r="B3" t="str">
+            <v>TOYOTA   TSUSHO  PHILIPPINES CORPORATION</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="3085">
+        <row r="3">
+          <cell r="B3" t="str">
+            <v>TOYOTA   TSUSHO  PHILIPPINES CORPORATION</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="3086">
+        <row r="3">
+          <cell r="B3" t="str">
+            <v>TOYOTA   TSUSHO  PHILIPPINES CORPORATION</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="3087">
+        <row r="3">
+          <cell r="B3" t="str">
+            <v>TOYOTA   TSUSHO  PHILIPPINES CORPORATION</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="3088">
+        <row r="3">
+          <cell r="B3" t="str">
+            <v>TOYOTA   TSUSHO  PHILIPPINES CORPORATION</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="3089">
+        <row r="3">
+          <cell r="B3" t="str">
+            <v>TOYOTA   TSUSHO  PHILIPPINES CORPORATION</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="3090">
+        <row r="3">
+          <cell r="B3" t="str">
+            <v>TOYOTA   TSUSHO  PHILIPPINES CORPORATION</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="3091">
+        <row r="3">
+          <cell r="B3" t="str">
+            <v>TOYOTA   TSUSHO  PHILIPPINES CORPORATION</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="3092">
+        <row r="3">
+          <cell r="B3" t="str">
+            <v>TOYOTA   TSUSHO  PHILIPPINES CORPORATION</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="3093">
+        <row r="3">
+          <cell r="B3" t="str">
+            <v>TOYOTA   TSUSHO  PHILIPPINES CORPORATION</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="3094">
+        <row r="3">
+          <cell r="B3" t="str">
+            <v>TOYOTA   TSUSHO  PHILIPPINES CORPORATION</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="3095">
+        <row r="3">
+          <cell r="B3" t="str">
+            <v>TOYOTA   TSUSHO  PHILIPPINES CORPORATION</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="3096">
+        <row r="3">
+          <cell r="B3" t="str">
+            <v>TOYOTA   TSUSHO  PHILIPPINES CORPORATION</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="3097">
+        <row r="3">
+          <cell r="B3" t="str">
+            <v>TOYOTA   TSUSHO  PHILIPPINES CORPORATION</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="3098">
+        <row r="3">
+          <cell r="B3" t="str">
+            <v>TOYOTA   TSUSHO  PHILIPPINES CORPORATION</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="3099">
+        <row r="3">
+          <cell r="B3" t="str">
+            <v>TOYOTA   TSUSHO  PHILIPPINES CORPORATION</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="3100"/>
+      <sheetData sheetId="3101"/>
+      <sheetData sheetId="3102"/>
+      <sheetData sheetId="3103"/>
+      <sheetData sheetId="3104"/>
+      <sheetData sheetId="3105"/>
+      <sheetData sheetId="3106"/>
+      <sheetData sheetId="3107"/>
+      <sheetData sheetId="3108"/>
+      <sheetData sheetId="3109"/>
+      <sheetData sheetId="3110"/>
+      <sheetData sheetId="3111"/>
+      <sheetData sheetId="3112"/>
+      <sheetData sheetId="3113"/>
+      <sheetData sheetId="3114"/>
+      <sheetData sheetId="3115"/>
+      <sheetData sheetId="3116"/>
+      <sheetData sheetId="3117"/>
+      <sheetData sheetId="3118"/>
+      <sheetData sheetId="3119"/>
+      <sheetData sheetId="3120"/>
+      <sheetData sheetId="3121"/>
+      <sheetData sheetId="3122"/>
+      <sheetData sheetId="3123"/>
+      <sheetData sheetId="3124"/>
+      <sheetData sheetId="3125"/>
+      <sheetData sheetId="3126"/>
+      <sheetData sheetId="3127"/>
+      <sheetData sheetId="3128"/>
+      <sheetData sheetId="3129"/>
+      <sheetData sheetId="3130"/>
+      <sheetData sheetId="3131"/>
+      <sheetData sheetId="3132"/>
+      <sheetData sheetId="3133"/>
+      <sheetData sheetId="3134"/>
+      <sheetData sheetId="3135"/>
+      <sheetData sheetId="3136"/>
+      <sheetData sheetId="3137" refreshError="1"/>
+      <sheetData sheetId="3138" refreshError="1"/>
+      <sheetData sheetId="3139" refreshError="1"/>
+      <sheetData sheetId="3140" refreshError="1"/>
+      <sheetData sheetId="3141" refreshError="1"/>
+      <sheetData sheetId="3142" refreshError="1"/>
+      <sheetData sheetId="3143" refreshError="1"/>
+      <sheetData sheetId="3144" refreshError="1"/>
+      <sheetData sheetId="3145" refreshError="1"/>
+      <sheetData sheetId="3146" refreshError="1"/>
+      <sheetData sheetId="3147" refreshError="1"/>
+      <sheetData sheetId="3148" refreshError="1"/>
+      <sheetData sheetId="3149" refreshError="1"/>
+      <sheetData sheetId="3150" refreshError="1"/>
+      <sheetData sheetId="3151" refreshError="1"/>
+      <sheetData sheetId="3152" refreshError="1"/>
+      <sheetData sheetId="3153" refreshError="1"/>
+      <sheetData sheetId="3154" refreshError="1"/>
+      <sheetData sheetId="3155" refreshError="1"/>
+      <sheetData sheetId="3156" refreshError="1"/>
+      <sheetData sheetId="3157" refreshError="1"/>
+      <sheetData sheetId="3158" refreshError="1"/>
+      <sheetData sheetId="3159" refreshError="1"/>
+      <sheetData sheetId="3160" refreshError="1"/>
+      <sheetData sheetId="3161" refreshError="1"/>
+      <sheetData sheetId="3162" refreshError="1"/>
+      <sheetData sheetId="3163" refreshError="1"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
@@ -27386,17 +28219,62 @@
       <sheetName val="_UnderConst_Analysis"/>
       <sheetName val="アップロード系(2)"/>
       <sheetName val="List"/>
+      <sheetName val="パラメータ設定表"/>
       <sheetName val="別紙7_操作系イベント発生時_"/>
       <sheetName val="別紙11_各競合条件における起動可否_"/>
       <sheetName val="index"/>
-      <sheetName val="パラメータ設定表"/>
+      <sheetName val="入力"/>
+      <sheetName val="415T戟L"/>
+      <sheetName val="No.31"/>
       <sheetName val="改訂履歴"/>
       <sheetName val="リスト"/>
       <sheetName val="ドメイン"/>
       <sheetName val="format"/>
-      <sheetName val="入力"/>
-      <sheetName val="415T戟L"/>
-      <sheetName val="No.31"/>
+      <sheetName val="Navigation"/>
+      <sheetName val="Cover"/>
+      <sheetName val="DataList"/>
+      <sheetName val="変更要件"/>
+      <sheetName val="【石倉編集中】DisplayStateTransitionTa"/>
+      <sheetName val="DetailSequence"/>
+      <sheetName val="R0-10表紙"/>
+      <sheetName val="Calcul"/>
+      <sheetName val="Data"/>
+      <sheetName val="★VarUsed"/>
+      <sheetName val="輝度計算(直線用)"/>
+      <sheetName val="コード_dimautocon"/>
+      <sheetName val="パラメータ_dimautocon"/>
+      <sheetName val="パラメータ_dimcalprcnt"/>
+      <sheetName val="パラメータ_dimmanualstep"/>
+      <sheetName val="パラメータ_dimmgr"/>
+      <sheetName val="XX-0080"/>
+      <sheetName val="メッセージ定義"/>
+      <sheetName val="XX-0180"/>
+      <sheetName val="lock"/>
+      <sheetName val="level"/>
+      <sheetName val="cominf"/>
+      <sheetName val="disconnect"/>
+      <sheetName val="９ｘ"/>
+      <sheetName val="Ｂｘ"/>
+      <sheetName val="Ｃｘ"/>
+      <sheetName val="Ｅｘ"/>
+      <sheetName val="休日"/>
+      <sheetName val="HMI-004_Screen（old）"/>
+      <sheetName val="ﾊﾟｲﾌﾟ"/>
+      <sheetName val="冷延鋼板"/>
+      <sheetName val="熱延鋼板"/>
+      <sheetName val="他材料費"/>
+      <sheetName val="MOTO"/>
+      <sheetName val="前提書情報"/>
+      <sheetName val="②P071中計　工数パターン1312更新"/>
+      <sheetName val="module"/>
+      <sheetName val="選択肢"/>
+      <sheetName val="vocabulary"/>
+      <sheetName val="メニュー"/>
+      <sheetName val="Calibration"/>
+      <sheetName val="R0-10表紙MIC"/>
+      <sheetName val="CVBS"/>
+      <sheetName val="修正ﾌｧｲﾙ一覧"/>
+      <sheetName val="RGB"/>
     </sheetNames>
     <sheetDataSet>
       <sheetData sheetId="0"/>
@@ -27495,6 +28373,51 @@
       <sheetData sheetId="93" refreshError="1"/>
       <sheetData sheetId="94" refreshError="1"/>
       <sheetData sheetId="95" refreshError="1"/>
+      <sheetData sheetId="96" refreshError="1"/>
+      <sheetData sheetId="97" refreshError="1"/>
+      <sheetData sheetId="98" refreshError="1"/>
+      <sheetData sheetId="99" refreshError="1"/>
+      <sheetData sheetId="100" refreshError="1"/>
+      <sheetData sheetId="101" refreshError="1"/>
+      <sheetData sheetId="102" refreshError="1"/>
+      <sheetData sheetId="103" refreshError="1"/>
+      <sheetData sheetId="104" refreshError="1"/>
+      <sheetData sheetId="105" refreshError="1"/>
+      <sheetData sheetId="106" refreshError="1"/>
+      <sheetData sheetId="107" refreshError="1"/>
+      <sheetData sheetId="108" refreshError="1"/>
+      <sheetData sheetId="109" refreshError="1"/>
+      <sheetData sheetId="110" refreshError="1"/>
+      <sheetData sheetId="111" refreshError="1"/>
+      <sheetData sheetId="112" refreshError="1"/>
+      <sheetData sheetId="113" refreshError="1"/>
+      <sheetData sheetId="114" refreshError="1"/>
+      <sheetData sheetId="115" refreshError="1"/>
+      <sheetData sheetId="116" refreshError="1"/>
+      <sheetData sheetId="117" refreshError="1"/>
+      <sheetData sheetId="118" refreshError="1"/>
+      <sheetData sheetId="119" refreshError="1"/>
+      <sheetData sheetId="120" refreshError="1"/>
+      <sheetData sheetId="121" refreshError="1"/>
+      <sheetData sheetId="122" refreshError="1"/>
+      <sheetData sheetId="123" refreshError="1"/>
+      <sheetData sheetId="124" refreshError="1"/>
+      <sheetData sheetId="125" refreshError="1"/>
+      <sheetData sheetId="126" refreshError="1"/>
+      <sheetData sheetId="127" refreshError="1"/>
+      <sheetData sheetId="128" refreshError="1"/>
+      <sheetData sheetId="129" refreshError="1"/>
+      <sheetData sheetId="130" refreshError="1"/>
+      <sheetData sheetId="131" refreshError="1"/>
+      <sheetData sheetId="132" refreshError="1"/>
+      <sheetData sheetId="133" refreshError="1"/>
+      <sheetData sheetId="134" refreshError="1"/>
+      <sheetData sheetId="135" refreshError="1"/>
+      <sheetData sheetId="136" refreshError="1"/>
+      <sheetData sheetId="137" refreshError="1"/>
+      <sheetData sheetId="138" refreshError="1"/>
+      <sheetData sheetId="139" refreshError="1"/>
+      <sheetData sheetId="140" refreshError="1"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
@@ -27791,10 +28714,10 @@
     <tabColor theme="5"/>
   </sheetPr>
   <dimension ref="C1:AM57"/>
-  <sheetFormatPr defaultColWidth="8.125" defaultRowHeight="15.75"/>
+  <sheetFormatPr defaultColWidth="8.08984375" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="52" width="2.125" style="261" customWidth="1"/>
-    <col min="53" max="16384" width="8.125" style="261"/>
+    <col min="1" max="52" width="2.08984375" style="261" customWidth="1"/>
+    <col min="53" max="16384" width="8.08984375" style="261"/>
   </cols>
   <sheetData>
     <row r="1" spans="6:20" ht="13.15" customHeight="1"/>
@@ -27853,31 +28776,31 @@
     </row>
     <row r="34" spans="3:39" ht="13.15" customHeight="1">
       <c r="Y34" s="264" t="s">
-        <v>400</v>
+        <v>421</v>
       </c>
     </row>
     <row r="35" spans="3:39" ht="13.15" customHeight="1">
-      <c r="Y35" s="284" t="s">
+      <c r="Y35" s="291" t="s">
+        <v>399</v>
+      </c>
+      <c r="Z35" s="292"/>
+      <c r="AA35" s="292"/>
+      <c r="AB35" s="292"/>
+      <c r="AC35" s="293"/>
+      <c r="AD35" s="291" t="s">
+        <v>400</v>
+      </c>
+      <c r="AE35" s="292"/>
+      <c r="AF35" s="292"/>
+      <c r="AG35" s="292"/>
+      <c r="AH35" s="293"/>
+      <c r="AI35" s="291" t="s">
         <v>401</v>
       </c>
-      <c r="Z35" s="285"/>
-      <c r="AA35" s="285"/>
-      <c r="AB35" s="285"/>
-      <c r="AC35" s="286"/>
-      <c r="AD35" s="284" t="s">
-        <v>402</v>
-      </c>
-      <c r="AE35" s="285"/>
-      <c r="AF35" s="285"/>
-      <c r="AG35" s="285"/>
-      <c r="AH35" s="286"/>
-      <c r="AI35" s="284" t="s">
-        <v>403</v>
-      </c>
-      <c r="AJ35" s="285"/>
-      <c r="AK35" s="285"/>
-      <c r="AL35" s="285"/>
-      <c r="AM35" s="286"/>
+      <c r="AJ35" s="292"/>
+      <c r="AK35" s="292"/>
+      <c r="AL35" s="292"/>
+      <c r="AM35" s="293"/>
     </row>
     <row r="36" spans="3:39" ht="13.15" customHeight="1">
       <c r="D36" s="265"/>
@@ -27923,21 +28846,21 @@
       <c r="Y38" s="270"/>
       <c r="Z38" s="265"/>
       <c r="AA38" s="266" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
       <c r="AB38" s="265"/>
       <c r="AC38" s="272"/>
       <c r="AD38" s="270"/>
       <c r="AE38" s="265"/>
       <c r="AF38" s="266" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
       <c r="AG38" s="265"/>
       <c r="AH38" s="272"/>
       <c r="AI38" s="273"/>
       <c r="AJ38" s="265"/>
       <c r="AK38" s="266" t="s">
-        <v>406</v>
+        <v>404</v>
       </c>
       <c r="AL38" s="265"/>
       <c r="AM38" s="272"/>
@@ -27972,31 +28895,31 @@
     <row r="41" spans="3:39" ht="13.15" customHeight="1"/>
     <row r="42" spans="3:39" ht="13.15" customHeight="1">
       <c r="Y42" s="264" t="s">
-        <v>407</v>
+        <v>405</v>
       </c>
     </row>
     <row r="43" spans="3:39" ht="13.15" customHeight="1">
-      <c r="Y43" s="284" t="s">
+      <c r="Y43" s="291" t="s">
+        <v>399</v>
+      </c>
+      <c r="Z43" s="292"/>
+      <c r="AA43" s="292"/>
+      <c r="AB43" s="292"/>
+      <c r="AC43" s="293"/>
+      <c r="AD43" s="291" t="s">
+        <v>400</v>
+      </c>
+      <c r="AE43" s="292"/>
+      <c r="AF43" s="292"/>
+      <c r="AG43" s="292"/>
+      <c r="AH43" s="293"/>
+      <c r="AI43" s="291" t="s">
         <v>401</v>
       </c>
-      <c r="Z43" s="285"/>
-      <c r="AA43" s="285"/>
-      <c r="AB43" s="285"/>
-      <c r="AC43" s="286"/>
-      <c r="AD43" s="284" t="s">
-        <v>402</v>
-      </c>
-      <c r="AE43" s="285"/>
-      <c r="AF43" s="285"/>
-      <c r="AG43" s="285"/>
-      <c r="AH43" s="286"/>
-      <c r="AI43" s="284" t="s">
-        <v>403</v>
-      </c>
-      <c r="AJ43" s="285"/>
-      <c r="AK43" s="285"/>
-      <c r="AL43" s="285"/>
-      <c r="AM43" s="286"/>
+      <c r="AJ43" s="292"/>
+      <c r="AK43" s="292"/>
+      <c r="AL43" s="292"/>
+      <c r="AM43" s="293"/>
     </row>
     <row r="44" spans="3:39" ht="13.15" customHeight="1">
       <c r="D44" s="265"/>
@@ -28042,21 +28965,21 @@
       <c r="Y46" s="270"/>
       <c r="Z46" s="265"/>
       <c r="AA46" s="266" t="s">
-        <v>408</v>
+        <v>406</v>
       </c>
       <c r="AB46" s="265"/>
       <c r="AC46" s="272"/>
       <c r="AD46" s="265"/>
       <c r="AE46" s="265"/>
       <c r="AF46" s="266" t="s">
-        <v>409</v>
+        <v>407</v>
       </c>
       <c r="AG46" s="265"/>
       <c r="AH46" s="272"/>
       <c r="AI46" s="273"/>
       <c r="AJ46" s="265"/>
       <c r="AK46" s="266" t="s">
-        <v>410</v>
+        <v>408</v>
       </c>
       <c r="AL46" s="265"/>
       <c r="AM46" s="272"/>
@@ -28090,31 +29013,31 @@
     <row r="49" spans="4:39" ht="13.15" customHeight="1"/>
     <row r="50" spans="4:39" ht="13.15" customHeight="1">
       <c r="Y50" s="264" t="s">
-        <v>411</v>
+        <v>409</v>
       </c>
     </row>
     <row r="51" spans="4:39" ht="13.15" customHeight="1">
-      <c r="Y51" s="284" t="s">
+      <c r="Y51" s="291" t="s">
+        <v>399</v>
+      </c>
+      <c r="Z51" s="292"/>
+      <c r="AA51" s="292"/>
+      <c r="AB51" s="292"/>
+      <c r="AC51" s="293"/>
+      <c r="AD51" s="291" t="s">
+        <v>400</v>
+      </c>
+      <c r="AE51" s="292"/>
+      <c r="AF51" s="292"/>
+      <c r="AG51" s="292"/>
+      <c r="AH51" s="293"/>
+      <c r="AI51" s="291" t="s">
         <v>401</v>
       </c>
-      <c r="Z51" s="285"/>
-      <c r="AA51" s="285"/>
-      <c r="AB51" s="285"/>
-      <c r="AC51" s="286"/>
-      <c r="AD51" s="284" t="s">
-        <v>402</v>
-      </c>
-      <c r="AE51" s="285"/>
-      <c r="AF51" s="285"/>
-      <c r="AG51" s="285"/>
-      <c r="AH51" s="286"/>
-      <c r="AI51" s="284" t="s">
-        <v>403</v>
-      </c>
-      <c r="AJ51" s="285"/>
-      <c r="AK51" s="285"/>
-      <c r="AL51" s="285"/>
-      <c r="AM51" s="286"/>
+      <c r="AJ51" s="292"/>
+      <c r="AK51" s="292"/>
+      <c r="AL51" s="292"/>
+      <c r="AM51" s="293"/>
     </row>
     <row r="52" spans="4:39" ht="13.15" customHeight="1">
       <c r="D52" s="265"/>
@@ -28160,21 +29083,21 @@
       <c r="Y54" s="270"/>
       <c r="Z54" s="265"/>
       <c r="AA54" s="266" t="s">
-        <v>412</v>
+        <v>410</v>
       </c>
       <c r="AB54" s="265"/>
       <c r="AC54" s="272"/>
       <c r="AD54" s="265"/>
       <c r="AE54" s="265"/>
       <c r="AF54" s="266" t="s">
-        <v>413</v>
+        <v>411</v>
       </c>
       <c r="AG54" s="265"/>
       <c r="AH54" s="272"/>
       <c r="AI54" s="273"/>
       <c r="AJ54" s="265"/>
       <c r="AK54" s="266" t="s">
-        <v>406</v>
+        <v>404</v>
       </c>
       <c r="AL54" s="265"/>
       <c r="AM54" s="272"/>
@@ -28205,7 +29128,7 @@
     </row>
     <row r="57" spans="4:39" ht="13.15" customHeight="1">
       <c r="AK57" s="261" t="s">
-        <v>414</v>
+        <v>412</v>
       </c>
     </row>
   </sheetData>
@@ -28234,14 +29157,14 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0800-000000000000}">
   <sheetPr codeName="Sheet6"/>
   <dimension ref="B2:D27"/>
-  <sheetFormatPr defaultRowHeight="13.5"/>
+  <sheetFormatPr defaultRowHeight="13"/>
   <cols>
-    <col min="2" max="2" width="4.875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.25" customWidth="1"/>
+    <col min="2" max="2" width="4.90625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.26953125" customWidth="1"/>
     <col min="4" max="4" width="86" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:4" ht="14.25" thickBot="1">
+    <row r="2" spans="2:4" ht="13.5" thickBot="1">
       <c r="B2" s="73" t="s">
         <v>82</v>
       </c>
@@ -28251,7 +29174,7 @@
       </c>
       <c r="D2" s="74"/>
     </row>
-    <row r="3" spans="2:4" ht="14.25" thickBot="1">
+    <row r="3" spans="2:4" ht="13.5" thickBot="1">
       <c r="B3" s="67" t="s">
         <v>80</v>
       </c>
@@ -28262,7 +29185,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="4" spans="2:4" ht="14.25" thickTop="1">
+    <row r="4" spans="2:4" ht="13.5" thickTop="1">
       <c r="B4" s="11">
         <v>0</v>
       </c>
@@ -28273,7 +29196,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="5" spans="2:4" ht="40.5">
+    <row r="5" spans="2:4" ht="39">
       <c r="B5" s="1">
         <v>1</v>
       </c>
@@ -28284,7 +29207,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="6" spans="2:4" ht="27">
+    <row r="6" spans="2:4" ht="26">
       <c r="B6" s="1">
         <v>2</v>
       </c>
@@ -28295,7 +29218,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="7" spans="2:4" ht="54">
+    <row r="7" spans="2:4" ht="52">
       <c r="B7" s="1">
         <v>3</v>
       </c>
@@ -28306,7 +29229,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="8" spans="2:4" ht="81">
+    <row r="8" spans="2:4" ht="78">
       <c r="B8" s="1">
         <v>4</v>
       </c>
@@ -28328,7 +29251,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="10" spans="2:4" ht="27">
+    <row r="10" spans="2:4" ht="26">
       <c r="B10" s="1">
         <v>6</v>
       </c>
@@ -28339,7 +29262,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="11" spans="2:4" ht="27">
+    <row r="11" spans="2:4" ht="26">
       <c r="B11" s="1">
         <v>7</v>
       </c>
@@ -28350,7 +29273,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="12" spans="2:4" ht="27">
+    <row r="12" spans="2:4" ht="26">
       <c r="B12" s="1">
         <v>8</v>
       </c>
@@ -28361,7 +29284,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="13" spans="2:4" ht="27">
+    <row r="13" spans="2:4" ht="26">
       <c r="B13" s="1">
         <v>9</v>
       </c>
@@ -28372,7 +29295,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="14" spans="2:4" ht="27">
+    <row r="14" spans="2:4" ht="26">
       <c r="B14" s="1">
         <v>10</v>
       </c>
@@ -28383,7 +29306,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="15" spans="2:4" ht="135">
+    <row r="15" spans="2:4" ht="130">
       <c r="B15" s="1">
         <v>11</v>
       </c>
@@ -28405,7 +29328,7 @@
         <v>159</v>
       </c>
     </row>
-    <row r="17" spans="2:4" ht="27">
+    <row r="17" spans="2:4" ht="26">
       <c r="B17" s="1">
         <v>13</v>
       </c>
@@ -28416,7 +29339,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="18" spans="2:4" ht="67.5">
+    <row r="18" spans="2:4" ht="91">
       <c r="B18" s="1">
         <v>14</v>
       </c>
@@ -28427,7 +29350,7 @@
         <v>164</v>
       </c>
     </row>
-    <row r="19" spans="2:4" ht="40.5">
+    <row r="19" spans="2:4" ht="39">
       <c r="B19" s="1">
         <v>15</v>
       </c>
@@ -28460,37 +29383,37 @@
         <v>188</v>
       </c>
     </row>
-    <row r="22" spans="2:4" ht="27">
+    <row r="22" spans="2:4" ht="26">
       <c r="B22" s="1">
         <v>18</v>
       </c>
       <c r="C22" s="77" t="s">
+        <v>270</v>
+      </c>
+      <c r="D22" s="79" t="s">
         <v>271</v>
       </c>
-      <c r="D22" s="79" t="s">
-        <v>272</v>
-      </c>
     </row>
-    <row r="23" spans="2:4" ht="27">
+    <row r="23" spans="2:4" ht="26">
       <c r="B23" s="1">
         <v>19</v>
       </c>
       <c r="C23" s="77" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="D23" s="79" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
     </row>
-    <row r="24" spans="2:4" ht="94.5">
+    <row r="24" spans="2:4" ht="91">
       <c r="B24" s="1">
         <v>20</v>
       </c>
       <c r="C24" s="77" t="s">
+        <v>390</v>
+      </c>
+      <c r="D24" s="79" t="s">
         <v>391</v>
-      </c>
-      <c r="D24" s="79" t="s">
-        <v>392</v>
       </c>
     </row>
     <row r="25" spans="2:4">
@@ -28503,7 +29426,7 @@
       <c r="C26" s="77"/>
       <c r="D26" s="66"/>
     </row>
-    <row r="27" spans="2:4" ht="14.25" thickBot="1">
+    <row r="27" spans="2:4" ht="13.5" thickBot="1">
       <c r="B27" s="2"/>
       <c r="C27" s="78"/>
       <c r="D27" s="4"/>
@@ -28521,15 +29444,15 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="B2:X17"/>
-  <sheetFormatPr defaultRowHeight="13.5"/>
+  <dimension ref="B2:X18"/>
+  <sheetFormatPr defaultRowHeight="13"/>
   <cols>
-    <col min="1" max="1" width="4.5" customWidth="1"/>
+    <col min="1" max="1" width="4.453125" customWidth="1"/>
     <col min="2" max="2" width="9" style="8" hidden="1" customWidth="1"/>
-    <col min="4" max="4" width="69.5" customWidth="1"/>
-    <col min="5" max="6" width="12.75" customWidth="1"/>
-    <col min="7" max="22" width="13.125" hidden="1" customWidth="1"/>
-    <col min="23" max="24" width="13.125" customWidth="1"/>
+    <col min="4" max="4" width="69.453125" customWidth="1"/>
+    <col min="5" max="6" width="12.7265625" customWidth="1"/>
+    <col min="7" max="22" width="13.08984375" hidden="1" customWidth="1"/>
+    <col min="23" max="24" width="13.08984375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="2" spans="2:24" ht="25.5" customHeight="1">
@@ -28540,18 +29463,18 @@
       <c r="H2" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="I2" s="287" t="s">
+      <c r="I2" s="294" t="s">
         <v>14</v>
       </c>
-      <c r="J2" s="287"/>
-      <c r="K2" s="287"/>
-      <c r="L2" s="287"/>
-      <c r="M2" s="287"/>
-      <c r="N2" s="287"/>
-      <c r="O2" s="287"/>
-      <c r="P2" s="287"/>
-      <c r="Q2" s="287"/>
-      <c r="R2" s="287"/>
+      <c r="J2" s="294"/>
+      <c r="K2" s="294"/>
+      <c r="L2" s="294"/>
+      <c r="M2" s="294"/>
+      <c r="N2" s="294"/>
+      <c r="O2" s="294"/>
+      <c r="P2" s="294"/>
+      <c r="Q2" s="294"/>
+      <c r="R2" s="294"/>
     </row>
     <row r="3" spans="2:24" ht="25.5" customHeight="1">
       <c r="C3" s="5"/>
@@ -28564,24 +29487,24 @@
       <c r="H3" s="7" t="s">
         <v>167</v>
       </c>
-      <c r="I3" s="288" t="s">
+      <c r="I3" s="295" t="s">
         <v>166</v>
       </c>
-      <c r="J3" s="289"/>
-      <c r="K3" s="289"/>
-      <c r="L3" s="289"/>
-      <c r="M3" s="289"/>
-      <c r="N3" s="289"/>
-      <c r="O3" s="289"/>
-      <c r="P3" s="289"/>
-      <c r="Q3" s="289"/>
-      <c r="R3" s="289"/>
+      <c r="J3" s="296"/>
+      <c r="K3" s="296"/>
+      <c r="L3" s="296"/>
+      <c r="M3" s="296"/>
+      <c r="N3" s="296"/>
+      <c r="O3" s="296"/>
+      <c r="P3" s="296"/>
+      <c r="Q3" s="296"/>
+      <c r="R3" s="296"/>
     </row>
     <row r="4" spans="2:24" ht="25.5" customHeight="1">
       <c r="C4" s="5"/>
       <c r="D4" s="5"/>
       <c r="E4" s="20" t="str">
-        <f>DGET(B8:C20,"Ver.",H4:H5)</f>
+        <f>DGET(B8:C21,"Ver.",H4:H5)</f>
         <v>1.6.1</v>
       </c>
       <c r="F4" s="5"/>
@@ -28595,46 +29518,46 @@
       <c r="E5" s="5"/>
       <c r="F5" s="5"/>
       <c r="H5" s="10">
-        <f>MAX(B9:B20)</f>
+        <f>MAX(B9:B21)</f>
         <v>8</v>
       </c>
     </row>
-    <row r="6" spans="2:24" ht="14.25" thickBot="1"/>
+    <row r="6" spans="2:24" ht="13.5" thickBot="1"/>
     <row r="7" spans="2:24">
-      <c r="C7" s="292" t="s">
-        <v>0</v>
-      </c>
-      <c r="D7" s="293"/>
-      <c r="E7" s="294" t="s">
+      <c r="C7" s="299" t="s">
+        <v>0</v>
+      </c>
+      <c r="D7" s="300"/>
+      <c r="E7" s="301" t="s">
         <v>2</v>
       </c>
-      <c r="F7" s="294"/>
-      <c r="G7" s="295" t="s">
+      <c r="F7" s="301"/>
+      <c r="G7" s="302" t="s">
         <v>5</v>
       </c>
-      <c r="H7" s="295"/>
-      <c r="I7" s="295"/>
-      <c r="J7" s="295"/>
-      <c r="K7" s="295"/>
-      <c r="L7" s="295"/>
-      <c r="M7" s="296" t="s">
+      <c r="H7" s="302"/>
+      <c r="I7" s="302"/>
+      <c r="J7" s="302"/>
+      <c r="K7" s="302"/>
+      <c r="L7" s="302"/>
+      <c r="M7" s="303" t="s">
         <v>12</v>
       </c>
-      <c r="N7" s="296"/>
-      <c r="O7" s="296"/>
-      <c r="P7" s="296"/>
-      <c r="Q7" s="296"/>
-      <c r="R7" s="297"/>
-      <c r="S7" s="290" t="s">
-        <v>415</v>
-      </c>
-      <c r="T7" s="290"/>
-      <c r="U7" s="290"/>
-      <c r="V7" s="290"/>
-      <c r="W7" s="290"/>
-      <c r="X7" s="291"/>
+      <c r="N7" s="303"/>
+      <c r="O7" s="303"/>
+      <c r="P7" s="303"/>
+      <c r="Q7" s="303"/>
+      <c r="R7" s="304"/>
+      <c r="S7" s="297" t="s">
+        <v>413</v>
+      </c>
+      <c r="T7" s="297"/>
+      <c r="U7" s="297"/>
+      <c r="V7" s="297"/>
+      <c r="W7" s="297"/>
+      <c r="X7" s="298"/>
     </row>
-    <row r="8" spans="2:24" ht="27.75" thickBot="1">
+    <row r="8" spans="2:24" ht="26.5" thickBot="1">
       <c r="B8" s="8" t="s">
         <v>15</v>
       </c>
@@ -28687,7 +29610,7 @@
         <v>11</v>
       </c>
       <c r="S8" s="15" t="s">
-        <v>416</v>
+        <v>414</v>
       </c>
       <c r="T8" s="15" t="s">
         <v>7</v>
@@ -28705,7 +29628,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="9" spans="2:24" ht="14.25" thickTop="1">
+    <row r="9" spans="2:24" ht="13.5" thickTop="1">
       <c r="B9" s="8">
         <f>IF(C9=0,0,ROW()-ROW($B$8))</f>
         <v>1</v>
@@ -28741,19 +29664,19 @@
         <v>29</v>
       </c>
       <c r="M9" s="282" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="N9" s="283">
         <v>43909</v>
       </c>
       <c r="O9" s="282" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="P9" s="283">
         <v>43909</v>
       </c>
       <c r="Q9" s="282" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="R9" s="283">
         <v>43900</v>
@@ -28777,16 +29700,16 @@
         <v>29</v>
       </c>
     </row>
-    <row r="10" spans="2:24" ht="40.5">
+    <row r="10" spans="2:24" ht="39">
       <c r="B10" s="8">
         <f t="shared" ref="B10:B12" si="0">IF(C10=0,0,ROW()-ROW($B$8))</f>
         <v>2</v>
       </c>
       <c r="C10" s="1" t="s">
+        <v>260</v>
+      </c>
+      <c r="D10" s="191" t="s">
         <v>261</v>
-      </c>
-      <c r="D10" s="191" t="s">
-        <v>262</v>
       </c>
       <c r="E10" s="12" t="s">
         <v>29</v>
@@ -28813,19 +29736,19 @@
         <v>29</v>
       </c>
       <c r="M10" s="12" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="N10" s="190">
         <v>44008</v>
       </c>
       <c r="O10" s="12" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="P10" s="190">
         <v>44008</v>
       </c>
       <c r="Q10" s="12" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="R10" s="190">
         <v>44008</v>
@@ -28849,16 +29772,16 @@
         <v>29</v>
       </c>
     </row>
-    <row r="11" spans="2:24" ht="54">
+    <row r="11" spans="2:24" ht="52">
       <c r="B11" s="8">
         <f t="shared" si="0"/>
         <v>3</v>
       </c>
       <c r="C11" s="1" t="s">
+        <v>262</v>
+      </c>
+      <c r="D11" s="191" t="s">
         <v>263</v>
-      </c>
-      <c r="D11" s="191" t="s">
-        <v>264</v>
       </c>
       <c r="E11" s="12" t="s">
         <v>29</v>
@@ -28885,19 +29808,19 @@
         <v>29</v>
       </c>
       <c r="M11" s="12" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="N11" s="190">
         <v>44034</v>
       </c>
       <c r="O11" s="12" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="P11" s="190">
         <v>44034</v>
       </c>
       <c r="Q11" s="12" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="R11" s="190">
         <v>44034</v>
@@ -28921,16 +29844,16 @@
         <v>29</v>
       </c>
     </row>
-    <row r="12" spans="2:24" ht="54">
+    <row r="12" spans="2:24" ht="52">
       <c r="B12" s="8">
         <f t="shared" si="0"/>
         <v>4</v>
       </c>
       <c r="C12" s="1" t="s">
+        <v>267</v>
+      </c>
+      <c r="D12" s="191" t="s">
         <v>268</v>
-      </c>
-      <c r="D12" s="191" t="s">
-        <v>269</v>
       </c>
       <c r="E12" s="12" t="s">
         <v>29</v>
@@ -28957,19 +29880,19 @@
         <v>29</v>
       </c>
       <c r="M12" s="12" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="N12" s="190">
         <v>44186</v>
       </c>
       <c r="O12" s="12" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="P12" s="190">
         <v>44186</v>
       </c>
       <c r="Q12" s="12" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="R12" s="190">
         <v>44186</v>
@@ -28993,22 +29916,22 @@
         <v>29</v>
       </c>
     </row>
-    <row r="13" spans="2:24" ht="67.5">
+    <row r="13" spans="2:24" ht="65">
       <c r="B13" s="8">
-        <f t="shared" ref="B13:B17" si="1">IF(C13=0,0,ROW()-ROW($B$8))</f>
+        <f t="shared" ref="B13:B18" si="1">IF(C13=0,0,ROW()-ROW($B$8))</f>
         <v>5</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="D13" s="191" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="E13" s="12" t="s">
         <v>29</v>
       </c>
       <c r="F13" s="12" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="G13" s="12" t="s">
         <v>29</v>
@@ -29033,7 +29956,7 @@
       <c r="O13" s="194"/>
       <c r="P13" s="194"/>
       <c r="Q13" s="194" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="R13" s="279">
         <v>44337</v>
@@ -29057,22 +29980,22 @@
         <v>29</v>
       </c>
     </row>
-    <row r="14" spans="2:24" ht="108">
+    <row r="14" spans="2:24" ht="104">
       <c r="B14" s="8">
         <f t="shared" si="1"/>
         <v>6</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="D14" s="191" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="E14" s="12" t="s">
         <v>29</v>
       </c>
       <c r="F14" s="12" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="G14" s="12" t="s">
         <v>29</v>
@@ -29097,7 +30020,7 @@
       <c r="O14" s="194"/>
       <c r="P14" s="194"/>
       <c r="Q14" s="194" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="R14" s="279">
         <v>44488</v>
@@ -29121,22 +30044,22 @@
         <v>29</v>
       </c>
     </row>
-    <row r="15" spans="2:24" ht="121.5">
+    <row r="15" spans="2:24" ht="117">
       <c r="B15" s="8">
         <f t="shared" ref="B15" si="2">IF(C15=0,0,ROW()-ROW($B$8))</f>
         <v>7</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="D15" s="191" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="E15" s="194" t="s">
         <v>29</v>
       </c>
       <c r="F15" s="194" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="G15" s="194" t="s">
         <v>29</v>
@@ -29161,7 +30084,7 @@
       <c r="O15" s="194"/>
       <c r="P15" s="194"/>
       <c r="Q15" s="194" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="R15" s="279">
         <v>44778</v>
@@ -29185,16 +30108,16 @@
         <v>29</v>
       </c>
     </row>
-    <row r="16" spans="2:24" ht="94.5">
+    <row r="16" spans="2:24" ht="91">
       <c r="B16" s="8">
         <f t="shared" si="1"/>
         <v>8</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>418</v>
+        <v>416</v>
       </c>
       <c r="D16" s="191" t="s">
-        <v>419</v>
+        <v>417</v>
       </c>
       <c r="E16" s="194" t="s">
         <v>29</v>
@@ -29231,39 +30154,75 @@
       <c r="U16" s="194"/>
       <c r="V16" s="279"/>
       <c r="W16" s="194" t="s">
-        <v>417</v>
+        <v>415</v>
       </c>
       <c r="X16" s="195">
         <v>45817</v>
       </c>
     </row>
-    <row r="17" spans="2:24" ht="14.25" thickBot="1">
-      <c r="B17" s="8">
+    <row r="17" spans="2:24" ht="91">
+      <c r="C17" s="286" t="s">
+        <v>418</v>
+      </c>
+      <c r="D17" s="287" t="s">
+        <v>422</v>
+      </c>
+      <c r="E17" s="288" t="s">
+        <v>29</v>
+      </c>
+      <c r="F17" s="288" t="s">
+        <v>29</v>
+      </c>
+      <c r="G17" s="284"/>
+      <c r="H17" s="284"/>
+      <c r="I17" s="284"/>
+      <c r="J17" s="284"/>
+      <c r="K17" s="284"/>
+      <c r="L17" s="284"/>
+      <c r="M17" s="284"/>
+      <c r="N17" s="284"/>
+      <c r="O17" s="284"/>
+      <c r="P17" s="284"/>
+      <c r="Q17" s="284"/>
+      <c r="R17" s="284"/>
+      <c r="S17" s="284"/>
+      <c r="T17" s="284"/>
+      <c r="U17" s="284"/>
+      <c r="V17" s="285"/>
+      <c r="W17" s="289" t="s">
+        <v>419</v>
+      </c>
+      <c r="X17" s="290">
+        <v>46008</v>
+      </c>
+    </row>
+    <row r="18" spans="2:24" ht="13.5" thickBot="1">
+      <c r="B18" s="8">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="C17" s="2"/>
-      <c r="D17" s="3"/>
-      <c r="E17" s="3"/>
-      <c r="F17" s="3"/>
-      <c r="G17" s="3"/>
-      <c r="H17" s="3"/>
-      <c r="I17" s="3"/>
-      <c r="J17" s="3"/>
-      <c r="K17" s="3"/>
-      <c r="L17" s="3"/>
-      <c r="M17" s="3"/>
-      <c r="N17" s="3"/>
-      <c r="O17" s="3"/>
-      <c r="P17" s="3"/>
-      <c r="Q17" s="3"/>
-      <c r="R17" s="3"/>
-      <c r="S17" s="3"/>
-      <c r="T17" s="3"/>
-      <c r="U17" s="3"/>
-      <c r="V17" s="3"/>
-      <c r="W17" s="3"/>
-      <c r="X17" s="258"/>
+      <c r="C18" s="2"/>
+      <c r="D18" s="3"/>
+      <c r="E18" s="3"/>
+      <c r="F18" s="3"/>
+      <c r="G18" s="3"/>
+      <c r="H18" s="3"/>
+      <c r="I18" s="3"/>
+      <c r="J18" s="3"/>
+      <c r="K18" s="3"/>
+      <c r="L18" s="3"/>
+      <c r="M18" s="3"/>
+      <c r="N18" s="3"/>
+      <c r="O18" s="3"/>
+      <c r="P18" s="3"/>
+      <c r="Q18" s="3"/>
+      <c r="R18" s="3"/>
+      <c r="S18" s="3"/>
+      <c r="T18" s="3"/>
+      <c r="U18" s="3"/>
+      <c r="V18" s="3"/>
+      <c r="W18" s="3"/>
+      <c r="X18" s="258"/>
     </row>
   </sheetData>
   <mergeCells count="7">
@@ -29288,11 +30247,11 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <sheetPr codeName="Sheet4"/>
   <dimension ref="B2:E39"/>
-  <sheetFormatPr defaultRowHeight="13.5"/>
+  <sheetFormatPr defaultRowHeight="13"/>
   <cols>
-    <col min="2" max="2" width="4.625" customWidth="1"/>
-    <col min="3" max="3" width="3.5" customWidth="1"/>
-    <col min="4" max="4" width="17.5" customWidth="1"/>
+    <col min="2" max="2" width="4.6328125" customWidth="1"/>
+    <col min="3" max="3" width="3.453125" customWidth="1"/>
+    <col min="4" max="4" width="17.453125" customWidth="1"/>
     <col min="5" max="5" width="106" customWidth="1"/>
   </cols>
   <sheetData>
@@ -29306,13 +30265,13 @@
         <v>136</v>
       </c>
     </row>
-    <row r="6" spans="2:5" ht="14.25" thickBot="1">
+    <row r="6" spans="2:5" ht="13.5" thickBot="1">
       <c r="B6" s="137" t="s">
         <v>127</v>
       </c>
       <c r="C6" s="137"/>
     </row>
-    <row r="7" spans="2:5" ht="14.25" thickBot="1">
+    <row r="7" spans="2:5" ht="13.5" thickBot="1">
       <c r="C7" s="67" t="s">
         <v>129</v>
       </c>
@@ -29329,7 +30288,7 @@
         <v>138</v>
       </c>
       <c r="E8" s="140" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
     </row>
     <row r="9" spans="2:5">
@@ -29337,7 +30296,7 @@
       <c r="D9" s="179"/>
       <c r="E9" s="148"/>
     </row>
-    <row r="10" spans="2:5" ht="14.25" thickBot="1">
+    <row r="10" spans="2:5" ht="13.5" thickBot="1">
       <c r="C10" s="145"/>
       <c r="D10" s="78"/>
       <c r="E10" s="4"/>
@@ -29345,14 +30304,14 @@
     <row r="11" spans="2:5">
       <c r="C11" s="143"/>
     </row>
-    <row r="12" spans="2:5" ht="14.25" thickBot="1">
+    <row r="12" spans="2:5" ht="13.5" thickBot="1">
       <c r="B12" s="138" t="s">
         <v>128</v>
       </c>
       <c r="C12" s="74"/>
       <c r="D12" s="74"/>
     </row>
-    <row r="13" spans="2:5" ht="14.25" thickBot="1">
+    <row r="13" spans="2:5" ht="13.5" thickBot="1">
       <c r="B13" s="139"/>
       <c r="C13" s="144" t="s">
         <v>129</v>
@@ -29364,7 +30323,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="14" spans="2:5" ht="14.25" thickTop="1">
+    <row r="14" spans="2:5" ht="13.5" thickTop="1">
       <c r="C14" s="141">
         <v>0</v>
       </c>
@@ -29441,17 +30400,17 @@
         <v>161</v>
       </c>
     </row>
-    <row r="21" spans="2:5" ht="14.25" thickBot="1">
+    <row r="21" spans="2:5" ht="13.5" thickBot="1">
       <c r="C21" s="145"/>
       <c r="D21" s="78"/>
       <c r="E21" s="4"/>
     </row>
-    <row r="24" spans="2:5" ht="14.25" thickBot="1">
+    <row r="24" spans="2:5" ht="13.5" thickBot="1">
       <c r="B24" s="137" t="s">
         <v>139</v>
       </c>
     </row>
-    <row r="25" spans="2:5" ht="14.25" thickBot="1">
+    <row r="25" spans="2:5" ht="13.5" thickBot="1">
       <c r="C25" s="144" t="s">
         <v>129</v>
       </c>
@@ -29538,26 +30497,26 @@
       <c r="D33" s="77"/>
       <c r="E33" s="66"/>
     </row>
-    <row r="34" spans="2:5" ht="14.25" thickBot="1">
+    <row r="34" spans="2:5" ht="13.5" thickBot="1">
       <c r="C34" s="145"/>
       <c r="D34" s="78"/>
       <c r="E34" s="4"/>
     </row>
-    <row r="37" spans="2:5" ht="14.25" thickBot="1">
+    <row r="37" spans="2:5" ht="13.5" thickBot="1">
       <c r="B37" s="137" t="s">
         <v>157</v>
       </c>
     </row>
     <row r="38" spans="2:5">
-      <c r="C38" s="298"/>
-      <c r="D38" s="299"/>
+      <c r="C38" s="305"/>
+      <c r="D38" s="306"/>
       <c r="E38" s="101" t="s">
         <v>118</v>
       </c>
     </row>
-    <row r="39" spans="2:5" ht="14.25" thickBot="1">
-      <c r="C39" s="300"/>
-      <c r="D39" s="301"/>
+    <row r="39" spans="2:5" ht="13.5" thickBot="1">
+      <c r="C39" s="307"/>
+      <c r="D39" s="308"/>
       <c r="E39" s="4" t="s">
         <v>119</v>
       </c>
@@ -29586,131 +30545,131 @@
     <tabColor rgb="FFCCFFCC"/>
   </sheetPr>
   <dimension ref="B1:N37"/>
-  <sheetFormatPr defaultRowHeight="13.5"/>
+  <sheetFormatPr defaultRowHeight="13"/>
   <cols>
-    <col min="2" max="2" width="3.75" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="9.125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="19.125" bestFit="1" customWidth="1"/>
-    <col min="6" max="8" width="26.75" customWidth="1"/>
-    <col min="9" max="9" width="20.875" hidden="1" customWidth="1"/>
+    <col min="2" max="2" width="3.7265625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.08984375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="19.08984375" bestFit="1" customWidth="1"/>
+    <col min="6" max="8" width="26.7265625" customWidth="1"/>
+    <col min="9" max="9" width="20.90625" hidden="1" customWidth="1"/>
     <col min="10" max="14" width="9" hidden="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:14" ht="14.25" thickBot="1"/>
+    <row r="1" spans="2:14" ht="13.5" thickBot="1"/>
     <row r="2" spans="2:14">
-      <c r="B2" s="314" t="s">
+      <c r="B2" s="321" t="s">
         <v>18</v>
       </c>
-      <c r="C2" s="315"/>
-      <c r="D2" s="302" t="s">
-        <v>397</v>
-      </c>
-      <c r="E2" s="303"/>
-      <c r="F2" s="303"/>
-      <c r="G2" s="303"/>
-      <c r="H2" s="304"/>
+      <c r="C2" s="322"/>
+      <c r="D2" s="309" t="s">
+        <v>396</v>
+      </c>
+      <c r="E2" s="310"/>
+      <c r="F2" s="310"/>
+      <c r="G2" s="310"/>
+      <c r="H2" s="311"/>
     </row>
     <row r="3" spans="2:14">
-      <c r="B3" s="316" t="s">
+      <c r="B3" s="323" t="s">
         <v>115</v>
       </c>
-      <c r="C3" s="317"/>
-      <c r="D3" s="320" t="s">
-        <v>398</v>
-      </c>
-      <c r="E3" s="321"/>
-      <c r="F3" s="321"/>
-      <c r="G3" s="321"/>
-      <c r="H3" s="322"/>
+      <c r="C3" s="324"/>
+      <c r="D3" s="327" t="s">
+        <v>397</v>
+      </c>
+      <c r="E3" s="328"/>
+      <c r="F3" s="328"/>
+      <c r="G3" s="328"/>
+      <c r="H3" s="329"/>
     </row>
-    <row r="4" spans="2:14" ht="14.25" thickBot="1">
-      <c r="B4" s="318" t="s">
+    <row r="4" spans="2:14" ht="13.5" thickBot="1">
+      <c r="B4" s="325" t="s">
         <v>17</v>
       </c>
-      <c r="C4" s="319"/>
-      <c r="D4" s="305" t="str">
+      <c r="C4" s="326"/>
+      <c r="D4" s="312" t="str">
         <f ca="1">表紙!D3&amp;".c"</f>
         <v>alert_B_WASLEV-CSTD-0-01-B-C1.c</v>
       </c>
-      <c r="E4" s="306"/>
-      <c r="F4" s="306"/>
-      <c r="G4" s="306"/>
-      <c r="H4" s="307"/>
+      <c r="E4" s="313"/>
+      <c r="F4" s="313"/>
+      <c r="G4" s="313"/>
+      <c r="H4" s="314"/>
     </row>
-    <row r="5" spans="2:14" ht="14.25" thickBot="1">
+    <row r="5" spans="2:14" ht="13.5" thickBot="1">
       <c r="D5" t="str">
         <f ca="1">IF(LEN(表紙!D3&amp;".c") = LENB(表紙!D3&amp;".c"),"※モジュール名 全角チェックOK","※モジュール名 全角チェックNG：ファイル名に全角文字が使用されています！")</f>
         <v>※モジュール名 全角チェックOK</v>
       </c>
     </row>
     <row r="6" spans="2:14">
-      <c r="B6" s="314" t="s">
+      <c r="B6" s="321" t="s">
         <v>34</v>
       </c>
-      <c r="C6" s="315"/>
-      <c r="D6" s="308" t="str">
+      <c r="C6" s="322"/>
+      <c r="D6" s="315" t="str">
         <f ca="1">MID(D4, LEN("alert_") + 1, FIND("-",D4,1) - LEN("alert_") - 1)</f>
         <v>B_WASLEV</v>
       </c>
-      <c r="E6" s="309"/>
-      <c r="F6" s="309"/>
-      <c r="G6" s="309"/>
-      <c r="H6" s="310"/>
+      <c r="E6" s="316"/>
+      <c r="F6" s="316"/>
+      <c r="G6" s="316"/>
+      <c r="H6" s="317"/>
     </row>
     <row r="7" spans="2:14">
-      <c r="B7" s="316" t="s">
+      <c r="B7" s="323" t="s">
         <v>35</v>
       </c>
-      <c r="C7" s="317"/>
-      <c r="D7" s="311">
+      <c r="C7" s="324"/>
+      <c r="D7" s="318">
         <f>COUNTA($D$13:$D$37)</f>
         <v>1</v>
       </c>
-      <c r="E7" s="312"/>
-      <c r="F7" s="312"/>
-      <c r="G7" s="312"/>
-      <c r="H7" s="313"/>
+      <c r="E7" s="319"/>
+      <c r="F7" s="319"/>
+      <c r="G7" s="319"/>
+      <c r="H7" s="320"/>
     </row>
     <row r="8" spans="2:14">
-      <c r="B8" s="316" t="s">
+      <c r="B8" s="323" t="s">
         <v>91</v>
       </c>
-      <c r="C8" s="317"/>
-      <c r="D8" s="311" t="str">
+      <c r="C8" s="324"/>
+      <c r="D8" s="318" t="str">
         <f ca="1">"st_gp_ALERT_"&amp;UPPER(D6)&amp;"_MTRX"</f>
         <v>st_gp_ALERT_B_WASLEV_MTRX</v>
       </c>
-      <c r="E8" s="312"/>
-      <c r="F8" s="312"/>
-      <c r="G8" s="312"/>
-      <c r="H8" s="313"/>
+      <c r="E8" s="319"/>
+      <c r="F8" s="319"/>
+      <c r="G8" s="319"/>
+      <c r="H8" s="320"/>
     </row>
     <row r="9" spans="2:14">
-      <c r="B9" s="316" t="s">
+      <c r="B9" s="323" t="s">
         <v>36</v>
       </c>
-      <c r="C9" s="317"/>
-      <c r="D9" s="323" t="s">
-        <v>210</v>
-      </c>
-      <c r="E9" s="324"/>
-      <c r="F9" s="324"/>
-      <c r="G9" s="324"/>
-      <c r="H9" s="325"/>
+      <c r="C9" s="324"/>
+      <c r="D9" s="330" t="s">
+        <v>209</v>
+      </c>
+      <c r="E9" s="331"/>
+      <c r="F9" s="331"/>
+      <c r="G9" s="331"/>
+      <c r="H9" s="332"/>
     </row>
-    <row r="10" spans="2:14" ht="14.25" thickBot="1">
-      <c r="B10" s="318" t="s">
+    <row r="10" spans="2:14" ht="13.5" thickBot="1">
+      <c r="B10" s="325" t="s">
         <v>42</v>
       </c>
-      <c r="C10" s="319"/>
-      <c r="D10" s="326"/>
-      <c r="E10" s="327"/>
-      <c r="F10" s="327"/>
-      <c r="G10" s="327"/>
-      <c r="H10" s="328"/>
+      <c r="C10" s="326"/>
+      <c r="D10" s="333"/>
+      <c r="E10" s="334"/>
+      <c r="F10" s="334"/>
+      <c r="G10" s="334"/>
+      <c r="H10" s="335"/>
     </row>
-    <row r="11" spans="2:14" ht="14.25" thickBot="1"/>
-    <row r="12" spans="2:14" ht="14.25" thickBot="1">
+    <row r="11" spans="2:14" ht="13.5" thickBot="1"/>
+    <row r="12" spans="2:14" ht="13.5" thickBot="1">
       <c r="B12" s="128" t="s">
         <v>32</v>
       </c>
@@ -29745,7 +30704,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="13" spans="2:14" ht="14.25" thickTop="1">
+    <row r="13" spans="2:14" ht="13.5" thickTop="1">
       <c r="B13" s="96">
         <v>1</v>
       </c>
@@ -29756,15 +30715,15 @@
         <v>46</v>
       </c>
       <c r="E13" s="178" t="s">
-        <v>195</v>
+        <v>420</v>
       </c>
       <c r="F13" s="43" t="str">
         <f t="shared" ref="F13:F37" ca="1" si="0">IF($D13&lt;&gt;"","u4_s_Alert"&amp;UPPER(LEFT($D$6,1))&amp;LOWER(MID($D$6,2,100))&amp;IF($D$7=1,"",N13)&amp;"Srcchk","")</f>
         <v>u4_s_AlertB_waslevSrcchk</v>
       </c>
       <c r="G13" s="43" t="str">
-        <f t="shared" ref="G13:G37" ca="1" si="1">IF($D13&lt;&gt;"",IF($E13="○","vd_s_Alert"&amp;UPPER(LEFT($D$6,1))&amp;LOWER(MID($D$6,2,100))&amp;IF($D$7=1,"",N13)&amp;"RwTx","NULL"),"")</f>
-        <v>vd_s_AlertB_waslevRwTx</v>
+        <f t="shared" ref="G13:G37" si="1">IF($D13&lt;&gt;"",IF($E13="○","vd_s_Alert"&amp;UPPER(LEFT($D$6,1))&amp;LOWER(MID($D$6,2,100))&amp;IF($D$7=1,"",N13)&amp;"RwTx","NULL"),"")</f>
+        <v>NULL</v>
       </c>
       <c r="H13" s="100" t="str">
         <f ca="1">IF($D13&lt;&gt;"","ALERT_CH_"&amp;UPPER($D$6)&amp;IF($D$7=1,"","_"&amp;UPPER($C13)),"")</f>
@@ -30598,7 +31557,7 @@
         <v/>
       </c>
     </row>
-    <row r="37" spans="2:14" ht="14.25" thickBot="1">
+    <row r="37" spans="2:14" ht="13.5" thickBot="1">
       <c r="B37" s="87">
         <v>25</v>
       </c>
@@ -30698,21 +31657,21 @@
     <tabColor rgb="FFCCFFCC"/>
   </sheetPr>
   <dimension ref="B2:R59"/>
-  <sheetFormatPr defaultRowHeight="13.5"/>
+  <sheetFormatPr defaultRowHeight="13"/>
   <cols>
-    <col min="2" max="2" width="3.75" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="19.125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="3.7265625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="19.08984375" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="13" customWidth="1"/>
-    <col min="5" max="5" width="36.5" customWidth="1"/>
-    <col min="6" max="6" width="52.75" customWidth="1"/>
-    <col min="7" max="7" width="7.125" bestFit="1" customWidth="1"/>
-    <col min="8" max="15" width="3.875" customWidth="1"/>
-    <col min="16" max="16" width="9.875" customWidth="1"/>
-    <col min="17" max="17" width="44.625" customWidth="1"/>
-    <col min="18" max="18" width="73.625" customWidth="1"/>
+    <col min="5" max="5" width="36.453125" customWidth="1"/>
+    <col min="6" max="6" width="52.7265625" customWidth="1"/>
+    <col min="7" max="7" width="7.08984375" bestFit="1" customWidth="1"/>
+    <col min="8" max="15" width="3.90625" customWidth="1"/>
+    <col min="16" max="16" width="9.90625" customWidth="1"/>
+    <col min="17" max="17" width="44.6328125" customWidth="1"/>
+    <col min="18" max="18" width="73.6328125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:18" ht="14.25" thickBot="1">
+    <row r="2" spans="2:18" ht="13.5" thickBot="1">
       <c r="B2" t="s">
         <v>184</v>
       </c>
@@ -30720,7 +31679,7 @@
         <v>186</v>
       </c>
     </row>
-    <row r="3" spans="2:18" ht="14.25" thickBot="1">
+    <row r="3" spans="2:18" ht="13.5" thickBot="1">
       <c r="B3" s="128" t="s">
         <v>32</v>
       </c>
@@ -30758,7 +31717,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="4" spans="2:18" ht="14.25" hidden="1" thickTop="1">
+    <row r="4" spans="2:18" ht="13.5" hidden="1" thickTop="1">
       <c r="B4" s="158">
         <v>0</v>
       </c>
@@ -30786,22 +31745,22 @@
       </c>
       <c r="R4" s="127"/>
     </row>
-    <row r="5" spans="2:18" ht="95.25" thickTop="1">
+    <row r="5" spans="2:18" ht="104.5" thickTop="1">
       <c r="B5" s="161">
         <v>1</v>
       </c>
       <c r="C5" s="132" t="s">
+        <v>280</v>
+      </c>
+      <c r="D5" s="21" t="s">
         <v>281</v>
-      </c>
-      <c r="D5" s="21" t="s">
-        <v>282</v>
       </c>
       <c r="E5" s="59" t="str">
         <f ca="1">IF($C5&lt;&gt;"","ALERT_" &amp; D5 &amp; "_ID_"&amp;UPPER(Matrix!$D$6) &amp; "_" &amp; $C5,"")</f>
         <v>ALERT_HW_ID_B_WASLEV_WLVL</v>
       </c>
       <c r="F5" s="197" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="G5" s="59">
         <f ca="1">IF(E5&lt;&gt;"",LEN(E5),"")</f>
@@ -31320,7 +32279,7 @@
       <c r="Q28" s="132"/>
       <c r="R28" s="105"/>
     </row>
-    <row r="29" spans="2:18" ht="14.25" thickBot="1">
+    <row r="29" spans="2:18" ht="13.5" thickBot="1">
       <c r="B29" s="162">
         <v>25</v>
       </c>
@@ -31342,7 +32301,7 @@
       <c r="Q29" s="130"/>
       <c r="R29" s="107"/>
     </row>
-    <row r="32" spans="2:18" ht="14.25" thickBot="1">
+    <row r="32" spans="2:18" ht="13.5" thickBot="1">
       <c r="B32" t="s">
         <v>185</v>
       </c>
@@ -31350,7 +32309,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="33" spans="2:18" ht="14.25" thickBot="1">
+    <row r="33" spans="2:18" ht="13.5" thickBot="1">
       <c r="B33" s="128" t="s">
         <v>32</v>
       </c>
@@ -31382,7 +32341,7 @@
         <v>174</v>
       </c>
     </row>
-    <row r="34" spans="2:18" ht="14.25" hidden="1" thickTop="1">
+    <row r="34" spans="2:18" ht="13.5" hidden="1" thickTop="1">
       <c r="B34" s="158">
         <v>0</v>
       </c>
@@ -31408,7 +32367,7 @@
         <v>158</v>
       </c>
     </row>
-    <row r="35" spans="2:18" ht="14.25" thickTop="1">
+    <row r="35" spans="2:18" ht="13.5" thickTop="1">
       <c r="B35" s="161">
         <v>1</v>
       </c>
@@ -31936,7 +32895,7 @@
       <c r="Q58" s="132"/>
       <c r="R58" s="163"/>
     </row>
-    <row r="59" spans="2:18" ht="14.25" thickBot="1">
+    <row r="59" spans="2:18" ht="13.5" thickBot="1">
       <c r="B59" s="162">
         <v>25</v>
       </c>
@@ -31987,29 +32946,29 @@
     <tabColor rgb="FFCCFFCC"/>
   </sheetPr>
   <dimension ref="B1:U103"/>
-  <sheetFormatPr defaultRowHeight="13.5"/>
+  <sheetFormatPr defaultRowHeight="13"/>
   <cols>
-    <col min="2" max="2" width="28.375" customWidth="1"/>
-    <col min="3" max="3" width="15.875" customWidth="1"/>
-    <col min="5" max="5" width="12.375" customWidth="1"/>
-    <col min="6" max="6" width="19.75" customWidth="1"/>
-    <col min="7" max="7" width="12.375" customWidth="1"/>
+    <col min="2" max="2" width="28.36328125" customWidth="1"/>
+    <col min="3" max="3" width="15.90625" customWidth="1"/>
+    <col min="5" max="5" width="12.36328125" customWidth="1"/>
+    <col min="6" max="6" width="19.7265625" customWidth="1"/>
+    <col min="7" max="7" width="12.36328125" customWidth="1"/>
     <col min="8" max="8" width="19" customWidth="1"/>
-    <col min="9" max="9" width="12.375" customWidth="1"/>
+    <col min="9" max="9" width="12.36328125" customWidth="1"/>
     <col min="10" max="10" width="31" customWidth="1"/>
-    <col min="11" max="11" width="12.375" customWidth="1"/>
-    <col min="12" max="12" width="16.125" customWidth="1"/>
-    <col min="14" max="14" width="30.125" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="57.125" hidden="1" customWidth="1"/>
+    <col min="11" max="11" width="12.36328125" customWidth="1"/>
+    <col min="12" max="12" width="16.08984375" customWidth="1"/>
+    <col min="14" max="14" width="30.08984375" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="57.08984375" hidden="1" customWidth="1"/>
     <col min="21" max="21" width="13" hidden="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:21" ht="14.25" thickBot="1">
+    <row r="1" spans="2:21" ht="13.5" thickBot="1">
       <c r="C1" s="80" t="s">
         <v>100</v>
       </c>
     </row>
-    <row r="2" spans="2:21" ht="14.25" thickBot="1">
+    <row r="2" spans="2:21" ht="13.5" thickBot="1">
       <c r="B2" s="88" t="s">
         <v>56</v>
       </c>
@@ -32053,7 +33012,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="3" spans="2:21" ht="15" hidden="1" thickTop="1" thickBot="1">
+    <row r="3" spans="2:21" ht="14" hidden="1" thickTop="1" thickBot="1">
       <c r="B3" s="22"/>
       <c r="C3" s="42" t="s">
         <v>104</v>
@@ -32074,39 +33033,39 @@
         <v>94</v>
       </c>
     </row>
-    <row r="4" spans="2:21" ht="14.25" thickTop="1">
+    <row r="4" spans="2:21" ht="13.5" thickTop="1">
       <c r="B4" s="22" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="C4" s="97" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="D4" s="108">
         <v>0</v>
       </c>
       <c r="E4" s="184" t="s">
+        <v>250</v>
+      </c>
+      <c r="F4" s="185" t="s">
         <v>251</v>
       </c>
-      <c r="F4" s="185" t="s">
-        <v>252</v>
-      </c>
       <c r="G4" s="184" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="H4" s="185" t="s">
         <v>29</v>
       </c>
       <c r="I4" s="184" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="J4" s="185" t="s">
         <v>29</v>
       </c>
       <c r="K4" s="184" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="L4" s="103" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="M4" s="43">
         <f ca="1">LEN(N4)</f>
@@ -32126,37 +33085,37 @@
     </row>
     <row r="5" spans="2:21">
       <c r="B5" s="99" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="C5" s="98" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="D5" s="109">
         <v>1</v>
       </c>
       <c r="E5" s="99" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="F5" s="186" t="s">
         <v>192</v>
       </c>
       <c r="G5" s="99" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="H5" s="186" t="s">
         <v>29</v>
       </c>
       <c r="I5" s="99" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="J5" s="105" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="K5" s="99" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="L5" s="186" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="M5" s="38">
         <f t="shared" ref="M5:M68" ca="1" si="1">LEN(N5)</f>
@@ -32176,37 +33135,37 @@
     </row>
     <row r="6" spans="2:21">
       <c r="B6" s="99" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="C6" s="97" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="D6" s="108">
         <v>2</v>
       </c>
       <c r="E6" s="99" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="F6" s="186" t="s">
         <v>154</v>
       </c>
       <c r="G6" s="99" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="H6" s="186" t="s">
         <v>29</v>
       </c>
       <c r="I6" s="99" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="J6" s="105" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="K6" s="99" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="L6" s="186" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="M6" s="38">
         <f t="shared" ca="1" si="1"/>
@@ -32386,7 +33345,7 @@
       </c>
       <c r="U12" s="27"/>
     </row>
-    <row r="13" spans="2:21" ht="14.25" thickBot="1">
+    <row r="13" spans="2:21" ht="13.5" thickBot="1">
       <c r="B13" s="22"/>
       <c r="C13" s="21"/>
       <c r="D13" s="104"/>
@@ -34637,7 +35596,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="103" spans="2:15" ht="14.25" thickBot="1">
+    <row r="103" spans="2:15" ht="13.5" thickBot="1">
       <c r="B103" s="44"/>
       <c r="C103" s="45"/>
       <c r="D103" s="106"/>
@@ -34710,18 +35669,18 @@
     <tabColor rgb="FFCCECFF"/>
   </sheetPr>
   <dimension ref="A1:AW199"/>
-  <sheetFormatPr defaultRowHeight="13.5"/>
+  <sheetFormatPr defaultRowHeight="13"/>
   <cols>
     <col min="1" max="1" width="6" customWidth="1"/>
-    <col min="2" max="2" width="16.75" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="16.7265625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="3" bestFit="1" customWidth="1"/>
     <col min="4" max="35" width="3" customWidth="1"/>
-    <col min="36" max="36" width="36.375" bestFit="1" customWidth="1"/>
-    <col min="37" max="37" width="4.125" customWidth="1"/>
+    <col min="36" max="36" width="36.36328125" bestFit="1" customWidth="1"/>
+    <col min="37" max="37" width="4.08984375" customWidth="1"/>
     <col min="38" max="42" width="9" hidden="1" customWidth="1"/>
-    <col min="43" max="43" width="20.625" hidden="1" customWidth="1"/>
-    <col min="44" max="47" width="41.125" customWidth="1"/>
-    <col min="48" max="48" width="23.625" customWidth="1"/>
+    <col min="43" max="43" width="20.6328125" hidden="1" customWidth="1"/>
+    <col min="44" max="47" width="41.08984375" customWidth="1"/>
+    <col min="48" max="48" width="23.6328125" customWidth="1"/>
     <col min="49" max="49" width="29" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -34737,7 +35696,7 @@
       <c r="B2" s="114" t="s">
         <v>123</v>
       </c>
-      <c r="C2" s="329" t="s">
+      <c r="C2" s="336" t="s">
         <v>79</v>
       </c>
       <c r="D2" s="49">
@@ -34836,8 +35795,8 @@
       <c r="AI2" s="49">
         <v>0</v>
       </c>
-      <c r="AJ2" s="331" t="s">
-        <v>260</v>
+      <c r="AJ2" s="338" t="s">
+        <v>259</v>
       </c>
     </row>
     <row r="3" spans="1:49" ht="213" customHeight="1" thickBot="1">
@@ -34845,7 +35804,7 @@
         <f>IF(OR(IF(COUNTIF(D6:AC69,"0")&lt;&gt;0,TRUE,FALSE),IF(COUNTIF(D6:AC69,"1")&lt;&gt;0,TRUE,FALSE)),"Search Table","Index Table")</f>
         <v>Index Table</v>
       </c>
-      <c r="C3" s="330"/>
+      <c r="C3" s="337"/>
       <c r="D3" s="116" t="s">
         <v>59</v>
       </c>
@@ -34928,28 +35887,28 @@
         <v>60</v>
       </c>
       <c r="AE3" s="198" t="s">
+        <v>286</v>
+      </c>
+      <c r="AF3" s="198" t="s">
         <v>287</v>
       </c>
-      <c r="AF3" s="198" t="s">
-        <v>288</v>
-      </c>
-      <c r="AG3" s="337" t="s">
-        <v>221</v>
-      </c>
-      <c r="AH3" s="338"/>
+      <c r="AG3" s="344" t="s">
+        <v>220</v>
+      </c>
+      <c r="AH3" s="345"/>
       <c r="AI3" s="183" t="s">
-        <v>248</v>
-      </c>
-      <c r="AJ3" s="332"/>
+        <v>247</v>
+      </c>
+      <c r="AJ3" s="339"/>
       <c r="AR3" s="81" t="s">
         <v>92</v>
       </c>
     </row>
-    <row r="4" spans="1:49" ht="14.25" thickBot="1">
-      <c r="A4" s="333" t="s">
+    <row r="4" spans="1:49" ht="13.5" thickBot="1">
+      <c r="A4" s="340" t="s">
         <v>61</v>
       </c>
-      <c r="B4" s="334"/>
+      <c r="B4" s="341"/>
       <c r="C4" s="174"/>
       <c r="D4" s="174"/>
       <c r="E4" s="174"/>
@@ -34993,9 +35952,9 @@
       <c r="AV4" s="70"/>
       <c r="AW4" s="71"/>
     </row>
-    <row r="5" spans="1:49" ht="14.25" thickBot="1">
-      <c r="A5" s="335"/>
-      <c r="B5" s="336"/>
+    <row r="5" spans="1:49" ht="13.5" thickBot="1">
+      <c r="A5" s="342"/>
+      <c r="B5" s="343"/>
       <c r="C5" s="175"/>
       <c r="D5" s="175"/>
       <c r="E5" s="175"/>
@@ -35177,7 +36136,7 @@
         <v xml:space="preserve">    (U1)ALERT_REQ_UNKNOWN,                                                     /* 00 UNKNOWN                                         */</v>
       </c>
       <c r="AU6" s="54" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="AV6" s="39" t="s">
         <v>66</v>
@@ -35290,7 +36249,7 @@
         <v>1</v>
       </c>
       <c r="AJ7" s="97" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="AL7" t="str">
         <f t="shared" ca="1" si="0"/>
@@ -35423,7 +36382,7 @@
         <v>0</v>
       </c>
       <c r="AJ8" s="97" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="AL8" t="str">
         <f t="shared" ca="1" si="0"/>
@@ -35443,7 +36402,7 @@
       </c>
       <c r="AU8" s="54" t="str">
         <f ca="1">IF($AW$15&lt;&gt;"NULL","        &amp;"&amp;$AW$15&amp;","&amp;REPT(" ",69-LEN($AW$15))&amp;"/* fp_vd_XDST                                         */","        vdp_PTR_NA,                                                            /* fp_vd_XDST                                         */")</f>
-        <v xml:space="preserve">        &amp;vd_s_AlertB_waslevRwTx,                                               /* fp_vd_XDST                                         */</v>
+        <v xml:space="preserve">        vdp_PTR_NA,                                                            /* fp_vd_XDST                                         */</v>
       </c>
       <c r="AV8" s="40" t="s">
         <v>68</v>
@@ -35556,7 +36515,7 @@
         <v>1</v>
       </c>
       <c r="AJ9" s="97" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="AL9" t="str">
         <f t="shared" ca="1" si="0"/>
@@ -35686,7 +36645,7 @@
         <v>0</v>
       </c>
       <c r="AJ10" s="97" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="AL10" t="str">
         <f t="shared" ca="1" si="0"/>
@@ -35819,7 +36778,7 @@
         <v>1</v>
       </c>
       <c r="AJ11" s="97" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="AL11" t="str">
         <f t="shared" ca="1" si="0"/>
@@ -36082,7 +37041,7 @@
         <v>1</v>
       </c>
       <c r="AJ13" s="97" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="AL13" t="str">
         <f t="shared" ca="1" si="0"/>
@@ -36215,7 +37174,7 @@
         <v>0</v>
       </c>
       <c r="AJ14" s="97" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="AL14" t="str">
         <f t="shared" ca="1" si="0"/>
@@ -36348,7 +37307,7 @@
         <v>1</v>
       </c>
       <c r="AJ15" s="97" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="AL15" t="str">
         <f t="shared" ca="1" si="0"/>
@@ -36375,7 +37334,7 @@
       </c>
       <c r="AW15" s="59" t="str">
         <f ca="1">IF(AW6&lt;&gt;AW17,VLOOKUP(AW6,Matrix!$C$13:$G$37,5,FALSE),Matrix!G13)</f>
-        <v>vd_s_AlertB_waslevRwTx</v>
+        <v>NULL</v>
       </c>
     </row>
     <row r="16" spans="1:49">
@@ -36481,7 +37440,7 @@
         <v>0</v>
       </c>
       <c r="AJ16" s="97" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="AL16" t="str">
         <f t="shared" ca="1" si="0"/>
@@ -36500,7 +37459,7 @@
         <v xml:space="preserve">    (U1)ALERT_REQ_B_WASLEV_TT_PD_ON,                                           /* 10 TT_PD_ON                                        */</v>
       </c>
       <c r="AU16" s="54" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="AV16" s="40" t="s">
         <v>74</v>
@@ -36510,7 +37469,7 @@
         <v>ALERT_VOM_IGN_ON</v>
       </c>
     </row>
-    <row r="17" spans="2:49" ht="14.25" thickBot="1">
+    <row r="17" spans="2:49" ht="13.5" thickBot="1">
       <c r="B17" s="123"/>
       <c r="C17" s="38">
         <f t="shared" si="2"/>
@@ -36613,7 +37572,7 @@
         <v>1</v>
       </c>
       <c r="AJ17" s="97" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="AL17" t="str">
         <f t="shared" ca="1" si="0"/>
@@ -36632,7 +37591,7 @@
         <v xml:space="preserve">    (U1)ALERT_REQ_B_WASLEV_TT_PD_ON,                                           /* 11 TT_PD_ON                                        */</v>
       </c>
       <c r="AU17" s="55" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="AV17" s="41" t="s">
         <v>75</v>
@@ -36745,7 +37704,7 @@
         <v>0</v>
       </c>
       <c r="AJ18" s="97" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="AL18" t="str">
         <f t="shared" ca="1" si="0"/>
@@ -36867,7 +37826,7 @@
         <v>1</v>
       </c>
       <c r="AJ19" s="97" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="AL19" t="str">
         <f t="shared" ca="1" si="0"/>
@@ -36989,7 +37948,7 @@
         <v>0</v>
       </c>
       <c r="AJ20" s="97" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="AL20" t="str">
         <f t="shared" ca="1" si="0"/>
@@ -37111,7 +38070,7 @@
         <v>1</v>
       </c>
       <c r="AJ21" s="97" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="AL21" t="str">
         <f t="shared" ca="1" si="0"/>
@@ -37233,7 +38192,7 @@
         <v>0</v>
       </c>
       <c r="AJ22" s="97" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="AL22" t="str">
         <f t="shared" ca="1" si="0"/>
@@ -37355,7 +38314,7 @@
         <v>1</v>
       </c>
       <c r="AJ23" s="97" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="AL23" t="str">
         <f t="shared" ca="1" si="0"/>
@@ -37477,7 +38436,7 @@
         <v>0</v>
       </c>
       <c r="AJ24" s="97" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="AL24" t="str">
         <f t="shared" ca="1" si="0"/>
@@ -37599,7 +38558,7 @@
         <v>1</v>
       </c>
       <c r="AJ25" s="97" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="AL25" t="str">
         <f t="shared" ca="1" si="0"/>
@@ -37721,7 +38680,7 @@
         <v>0</v>
       </c>
       <c r="AJ26" s="97" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="AL26" t="str">
         <f t="shared" ca="1" si="0"/>
@@ -37843,7 +38802,7 @@
         <v>1</v>
       </c>
       <c r="AJ27" s="97" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="AL27" t="str">
         <f t="shared" ca="1" si="0"/>
@@ -37965,7 +38924,7 @@
         <v>0</v>
       </c>
       <c r="AJ28" s="97" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="AL28" t="str">
         <f t="shared" ca="1" si="0"/>
@@ -38087,7 +39046,7 @@
         <v>1</v>
       </c>
       <c r="AJ29" s="97" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="AL29" t="str">
         <f t="shared" ca="1" si="0"/>
@@ -38209,7 +39168,7 @@
         <v>0</v>
       </c>
       <c r="AJ30" s="97" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="AL30" t="str">
         <f t="shared" ca="1" si="0"/>
@@ -38331,7 +39290,7 @@
         <v>1</v>
       </c>
       <c r="AJ31" s="97" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="AL31" t="str">
         <f t="shared" ca="1" si="0"/>
@@ -38453,7 +39412,7 @@
         <v>0</v>
       </c>
       <c r="AJ32" s="97" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="AL32" t="str">
         <f t="shared" ca="1" si="0"/>
@@ -38575,7 +39534,7 @@
         <v>1</v>
       </c>
       <c r="AJ33" s="97" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="AL33" t="str">
         <f t="shared" ca="1" si="0"/>
@@ -38697,7 +39656,7 @@
         <v>0</v>
       </c>
       <c r="AJ34" s="97" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="AL34" t="str">
         <f t="shared" ca="1" si="0"/>
@@ -38819,7 +39778,7 @@
         <v>1</v>
       </c>
       <c r="AJ35" s="97" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="AL35" t="str">
         <f t="shared" ca="1" si="0"/>
@@ -38941,7 +39900,7 @@
         <v>0</v>
       </c>
       <c r="AJ36" s="97" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="AL36" t="str">
         <f t="shared" ca="1" si="0"/>
@@ -39063,7 +40022,7 @@
         <v>1</v>
       </c>
       <c r="AJ37" s="97" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="AL37" t="str">
         <f t="shared" ca="1" si="0"/>
@@ -42922,7 +43881,7 @@
         <v/>
       </c>
     </row>
-    <row r="70" spans="1:46" ht="14.25" thickBot="1">
+    <row r="70" spans="1:46" ht="13.5" thickBot="1">
       <c r="A70" s="47" t="s">
         <v>62</v>
       </c>
@@ -63507,9 +64466,6 @@
     <protectedRange sqref="AI3" name="Table作成編集範囲_1_1"/>
     <protectedRange sqref="B3" name="Table作成編集範囲_1_2"/>
   </protectedRanges>
-  <autoFilter ref="A5:AW199" xr:uid="{00000000-0009-0000-0000-000005000000}">
-    <filterColumn colId="0" showButton="0"/>
-  </autoFilter>
   <mergeCells count="4">
     <mergeCell ref="C2:C3"/>
     <mergeCell ref="AJ2:AJ3"/>
@@ -63570,41 +64526,41 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
   <dimension ref="B2:BG42"/>
-  <sheetFormatPr defaultRowHeight="13.5"/>
+  <sheetFormatPr defaultRowHeight="13"/>
   <cols>
-    <col min="2" max="2" width="135.375" customWidth="1"/>
-    <col min="3" max="10" width="3.375" customWidth="1"/>
-    <col min="11" max="11" width="31.375" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="31.25" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="19.625" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.875" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="22.375" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="16.375" customWidth="1"/>
-    <col min="17" max="17" width="25.625" customWidth="1"/>
-    <col min="18" max="18" width="24.25" bestFit="1" customWidth="1"/>
-    <col min="19" max="21" width="18.125" customWidth="1"/>
-    <col min="22" max="22" width="16.875" customWidth="1"/>
+    <col min="2" max="2" width="135.36328125" customWidth="1"/>
+    <col min="3" max="10" width="3.36328125" customWidth="1"/>
+    <col min="11" max="11" width="31.36328125" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="31.26953125" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="19.6328125" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.90625" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="22.36328125" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="16.36328125" customWidth="1"/>
+    <col min="17" max="17" width="25.6328125" customWidth="1"/>
+    <col min="18" max="18" width="24.26953125" bestFit="1" customWidth="1"/>
+    <col min="19" max="21" width="18.08984375" customWidth="1"/>
+    <col min="22" max="22" width="16.90625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:59" ht="15" thickBot="1">
+    <row r="2" spans="2:59" ht="14.5" thickBot="1">
       <c r="B2" s="23" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
     </row>
-    <row r="3" spans="2:59" ht="15" thickBot="1">
+    <row r="3" spans="2:59" ht="14.5" thickBot="1">
       <c r="B3" s="85" t="s">
         <v>123</v>
       </c>
-      <c r="C3" s="339" t="s">
-        <v>298</v>
-      </c>
-      <c r="D3" s="340"/>
-      <c r="E3" s="340"/>
-      <c r="F3" s="340"/>
-      <c r="G3" s="340"/>
-      <c r="H3" s="340"/>
-      <c r="I3" s="340"/>
-      <c r="J3" s="341"/>
+      <c r="C3" s="346" t="s">
+        <v>297</v>
+      </c>
+      <c r="D3" s="347"/>
+      <c r="E3" s="347"/>
+      <c r="F3" s="347"/>
+      <c r="G3" s="347"/>
+      <c r="H3" s="347"/>
+      <c r="I3" s="347"/>
+      <c r="J3" s="348"/>
       <c r="K3" s="154"/>
       <c r="L3" s="154"/>
       <c r="M3" s="154"/>
@@ -63619,7 +64575,7 @@
     <row r="4" spans="2:59">
       <c r="B4" s="61"/>
       <c r="C4" s="30" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="D4" s="30"/>
       <c r="E4" s="30"/>
@@ -63646,27 +64602,27 @@
       <c r="B5" s="62" t="s">
         <v>21</v>
       </c>
-      <c r="C5" s="342" t="s">
+      <c r="C5" s="349" t="s">
         <v>161</v>
       </c>
-      <c r="D5" s="343"/>
-      <c r="E5" s="343"/>
-      <c r="F5" s="343"/>
-      <c r="G5" s="343"/>
-      <c r="H5" s="343"/>
-      <c r="I5" s="343"/>
-      <c r="J5" s="344"/>
+      <c r="D5" s="350"/>
+      <c r="E5" s="350"/>
+      <c r="F5" s="350"/>
+      <c r="G5" s="350"/>
+      <c r="H5" s="350"/>
+      <c r="I5" s="350"/>
+      <c r="J5" s="351"/>
       <c r="K5" s="235" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="L5" s="259"/>
       <c r="M5" s="235"/>
       <c r="N5" s="203"/>
       <c r="O5" s="204" t="s">
+        <v>213</v>
+      </c>
+      <c r="P5" s="205" t="s">
         <v>214</v>
-      </c>
-      <c r="P5" s="205" t="s">
-        <v>215</v>
       </c>
       <c r="Q5" s="205" t="s">
         <v>156</v>
@@ -63679,7 +64635,7 @@
       </c>
       <c r="BG5" s="196"/>
     </row>
-    <row r="6" spans="2:59" ht="27">
+    <row r="6" spans="2:59" ht="26">
       <c r="B6" s="62" t="s">
         <v>31</v>
       </c>
@@ -63726,23 +64682,23 @@
       <c r="Q6" s="208"/>
       <c r="R6" s="209"/>
       <c r="S6" s="210" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
     </row>
-    <row r="7" spans="2:59" ht="27">
+    <row r="7" spans="2:59" ht="26">
       <c r="B7" s="63" t="s">
         <v>26</v>
       </c>
-      <c r="C7" s="345" t="s">
+      <c r="C7" s="352" t="s">
         <v>33</v>
       </c>
-      <c r="D7" s="343"/>
-      <c r="E7" s="343"/>
-      <c r="F7" s="343"/>
-      <c r="G7" s="343"/>
-      <c r="H7" s="343"/>
-      <c r="I7" s="343"/>
-      <c r="J7" s="344"/>
+      <c r="D7" s="350"/>
+      <c r="E7" s="350"/>
+      <c r="F7" s="350"/>
+      <c r="G7" s="350"/>
+      <c r="H7" s="350"/>
+      <c r="I7" s="350"/>
+      <c r="J7" s="351"/>
       <c r="K7" s="207" t="s">
         <v>154</v>
       </c>
@@ -63760,60 +64716,60 @@
       <c r="Q7" s="208"/>
       <c r="R7" s="209"/>
       <c r="S7" s="206" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
     </row>
-    <row r="8" spans="2:59" ht="136.5">
+    <row r="8" spans="2:59" ht="131">
       <c r="B8" s="62" t="s">
         <v>27</v>
       </c>
       <c r="C8" s="150" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="D8" s="150" t="s">
         <v>60</v>
       </c>
       <c r="E8" s="150" t="s">
+        <v>198</v>
+      </c>
+      <c r="F8" s="150" t="s">
         <v>199</v>
       </c>
-      <c r="F8" s="150" t="s">
+      <c r="G8" s="150" t="s">
         <v>200</v>
       </c>
-      <c r="G8" s="150" t="s">
+      <c r="H8" s="150" t="s">
         <v>201</v>
       </c>
-      <c r="H8" s="150" t="s">
+      <c r="I8" s="150" t="s">
         <v>202</v>
       </c>
-      <c r="I8" s="150" t="s">
+      <c r="J8" s="150" t="s">
         <v>203</v>
       </c>
-      <c r="J8" s="150" t="s">
+      <c r="K8" s="212" t="s">
+        <v>289</v>
+      </c>
+      <c r="L8" s="212" t="s">
+        <v>288</v>
+      </c>
+      <c r="M8" s="212" t="s">
+        <v>220</v>
+      </c>
+      <c r="N8" s="213" t="s">
+        <v>221</v>
+      </c>
+      <c r="O8" s="204" t="s">
         <v>204</v>
-      </c>
-      <c r="K8" s="212" t="s">
-        <v>290</v>
-      </c>
-      <c r="L8" s="212" t="s">
-        <v>289</v>
-      </c>
-      <c r="M8" s="212" t="s">
-        <v>221</v>
-      </c>
-      <c r="N8" s="213" t="s">
-        <v>222</v>
-      </c>
-      <c r="O8" s="204" t="s">
-        <v>205</v>
       </c>
       <c r="P8" s="208"/>
       <c r="Q8" s="208"/>
       <c r="R8" s="209"/>
       <c r="S8" s="214" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="T8" s="179" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
     </row>
     <row r="9" spans="2:59" ht="117.75" customHeight="1" thickBot="1">
@@ -63821,58 +64777,58 @@
         <v>28</v>
       </c>
       <c r="C9" s="151" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="D9" s="151" t="s">
         <v>154</v>
       </c>
       <c r="E9" s="151" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="F9" s="151" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="G9" s="151" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="H9" s="151" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="I9" s="151" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="J9" s="151" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="K9" s="215" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="L9" s="215" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="M9" s="215" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="N9" s="216" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="O9" s="217" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="P9" s="218" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="Q9" s="218" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="R9" s="219"/>
       <c r="S9" s="220" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
     </row>
-    <row r="10" spans="2:59" ht="14.25" thickTop="1">
+    <row r="10" spans="2:59" ht="13.5" thickTop="1">
       <c r="B10" s="65" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="C10" s="152" t="s">
         <v>155</v>
@@ -63899,16 +64855,16 @@
         <v>155</v>
       </c>
       <c r="K10" s="221" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="L10" s="222" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="M10" s="221" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="N10" s="221" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="O10" s="223" t="s">
         <v>30</v>
@@ -63926,7 +64882,7 @@
     </row>
     <row r="11" spans="2:59">
       <c r="B11" s="65" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="C11" s="153" t="s">
         <v>155</v>
@@ -63953,22 +64909,22 @@
         <v>155</v>
       </c>
       <c r="K11" s="221" t="s">
+        <v>292</v>
+      </c>
+      <c r="L11" s="222" t="s">
+        <v>207</v>
+      </c>
+      <c r="M11" s="221" t="s">
         <v>293</v>
       </c>
-      <c r="L11" s="222" t="s">
+      <c r="N11" s="221" t="s">
         <v>208</v>
       </c>
-      <c r="M11" s="221" t="s">
-        <v>294</v>
-      </c>
-      <c r="N11" s="221" t="s">
-        <v>209</v>
-      </c>
       <c r="O11" s="189" t="s">
+        <v>226</v>
+      </c>
+      <c r="P11" s="227" t="s">
         <v>227</v>
-      </c>
-      <c r="P11" s="227" t="s">
-        <v>228</v>
       </c>
       <c r="Q11" s="227" t="s">
         <v>154</v>
@@ -63980,7 +64936,7 @@
     </row>
     <row r="12" spans="2:59">
       <c r="B12" s="65" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="C12" s="153" t="s">
         <v>155</v>
@@ -64007,34 +64963,34 @@
         <v>155</v>
       </c>
       <c r="K12" s="221" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="L12" s="222" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="M12" s="221" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="N12" s="221" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="O12" s="189" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="P12" s="227" t="s">
         <v>154</v>
       </c>
       <c r="Q12" s="227" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="R12" s="228"/>
       <c r="S12" s="229" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
     </row>
     <row r="13" spans="2:59">
       <c r="B13" s="65" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="C13" s="153" t="s">
         <v>155</v>
@@ -64061,34 +65017,34 @@
         <v>155</v>
       </c>
       <c r="K13" s="221" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="L13" s="222" t="s">
+        <v>207</v>
+      </c>
+      <c r="M13" s="221" t="s">
+        <v>231</v>
+      </c>
+      <c r="N13" s="221" t="s">
         <v>208</v>
       </c>
-      <c r="M13" s="221" t="s">
-        <v>232</v>
-      </c>
-      <c r="N13" s="221" t="s">
-        <v>209</v>
-      </c>
       <c r="O13" s="189" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="P13" s="227" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="Q13" s="227" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="R13" s="228"/>
       <c r="S13" s="229" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
     </row>
     <row r="14" spans="2:59">
       <c r="B14" s="65" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="C14" s="152" t="s">
         <v>155</v>
@@ -64115,34 +65071,34 @@
         <v>155</v>
       </c>
       <c r="K14" s="221" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="L14" s="222" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="M14" s="222" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="N14" s="221" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="O14" s="189" t="s">
+        <v>232</v>
+      </c>
+      <c r="P14" s="227" t="s">
+        <v>290</v>
+      </c>
+      <c r="Q14" s="227" t="s">
         <v>233</v>
-      </c>
-      <c r="P14" s="227" t="s">
-        <v>291</v>
-      </c>
-      <c r="Q14" s="227" t="s">
-        <v>234</v>
       </c>
       <c r="R14" s="228"/>
       <c r="S14" s="229" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
     </row>
     <row r="15" spans="2:59">
       <c r="B15" s="65" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="C15" s="153" t="s">
         <v>155</v>
@@ -64169,34 +65125,34 @@
         <v>155</v>
       </c>
       <c r="K15" s="221" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="L15" s="222" t="s">
+        <v>207</v>
+      </c>
+      <c r="M15" s="222" t="s">
+        <v>235</v>
+      </c>
+      <c r="N15" s="221" t="s">
         <v>208</v>
       </c>
-      <c r="M15" s="222" t="s">
-        <v>236</v>
-      </c>
-      <c r="N15" s="221" t="s">
-        <v>209</v>
-      </c>
       <c r="O15" s="189" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="P15" s="227" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="Q15" s="227" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="R15" s="228"/>
       <c r="S15" s="229" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
     </row>
     <row r="16" spans="2:59">
       <c r="B16" s="65" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="C16" s="153" t="s">
         <v>155</v>
@@ -64223,19 +65179,19 @@
         <v>155</v>
       </c>
       <c r="K16" s="221" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="L16" s="222" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="M16" s="222" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="N16" s="221" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="O16" s="189" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="P16" s="227" t="s">
         <v>154</v>
@@ -64250,7 +65206,7 @@
     </row>
     <row r="17" spans="2:19">
       <c r="B17" s="65" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="C17" s="153" t="s">
         <v>155</v>
@@ -64277,34 +65233,34 @@
         <v>155</v>
       </c>
       <c r="K17" s="221" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="L17" s="222" t="s">
+        <v>207</v>
+      </c>
+      <c r="M17" s="222" t="s">
+        <v>237</v>
+      </c>
+      <c r="N17" s="221" t="s">
         <v>208</v>
       </c>
-      <c r="M17" s="222" t="s">
-        <v>238</v>
-      </c>
-      <c r="N17" s="221" t="s">
-        <v>209</v>
-      </c>
       <c r="O17" s="189" t="s">
+        <v>226</v>
+      </c>
+      <c r="P17" s="227" t="s">
         <v>227</v>
       </c>
-      <c r="P17" s="227" t="s">
-        <v>228</v>
-      </c>
       <c r="Q17" s="227" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="R17" s="228"/>
       <c r="S17" s="229" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
     </row>
     <row r="18" spans="2:19">
       <c r="B18" s="65" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="C18" s="152" t="s">
         <v>155</v>
@@ -64331,34 +65287,34 @@
         <v>155</v>
       </c>
       <c r="K18" s="221" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="L18" s="221" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="M18" s="221" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="N18" s="221" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="O18" s="189" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="P18" s="227" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="Q18" s="227" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="R18" s="228"/>
       <c r="S18" s="229" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
     </row>
     <row r="19" spans="2:19">
       <c r="B19" s="65" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="C19" s="153" t="s">
         <v>155</v>
@@ -64385,34 +65341,34 @@
         <v>155</v>
       </c>
       <c r="K19" s="221" t="s">
+        <v>292</v>
+      </c>
+      <c r="L19" s="221" t="s">
+        <v>285</v>
+      </c>
+      <c r="M19" s="221" t="s">
         <v>293</v>
       </c>
-      <c r="L19" s="221" t="s">
-        <v>286</v>
-      </c>
-      <c r="M19" s="221" t="s">
-        <v>294</v>
-      </c>
       <c r="N19" s="221" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="O19" s="189" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="P19" s="227" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="Q19" s="227" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="R19" s="228"/>
       <c r="S19" s="229" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
     </row>
     <row r="20" spans="2:19">
       <c r="B20" s="65" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="C20" s="153" t="s">
         <v>155</v>
@@ -64439,34 +65395,34 @@
         <v>155</v>
       </c>
       <c r="K20" s="221" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="L20" s="221" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="M20" s="221" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="N20" s="221" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="O20" s="189" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="P20" s="227" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="Q20" s="227" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="R20" s="228"/>
       <c r="S20" s="229" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
     </row>
     <row r="21" spans="2:19">
       <c r="B21" s="65" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="C21" s="153" t="s">
         <v>155</v>
@@ -64493,34 +65449,34 @@
         <v>155</v>
       </c>
       <c r="K21" s="221" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="L21" s="221" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="M21" s="221" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="N21" s="221" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="O21" s="189" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="P21" s="227" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="Q21" s="227" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="R21" s="228"/>
       <c r="S21" s="229" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
     </row>
     <row r="22" spans="2:19">
       <c r="B22" s="65" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="C22" s="152" t="s">
         <v>155</v>
@@ -64547,34 +65503,34 @@
         <v>155</v>
       </c>
       <c r="K22" s="221" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="L22" s="221" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="M22" s="222" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="N22" s="221" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="O22" s="189" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="P22" s="227" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="Q22" s="227" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="R22" s="228"/>
       <c r="S22" s="229" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
     </row>
     <row r="23" spans="2:19">
       <c r="B23" s="65" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="C23" s="153" t="s">
         <v>155</v>
@@ -64601,34 +65557,34 @@
         <v>155</v>
       </c>
       <c r="K23" s="221" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="L23" s="221" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="M23" s="222" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="N23" s="221" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="O23" s="189" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="P23" s="227" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="Q23" s="227" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="R23" s="228"/>
       <c r="S23" s="229" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
     </row>
     <row r="24" spans="2:19">
       <c r="B24" s="65" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="C24" s="153" t="s">
         <v>155</v>
@@ -64655,34 +65611,34 @@
         <v>155</v>
       </c>
       <c r="K24" s="221" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="L24" s="221" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="M24" s="222" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="N24" s="221" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="O24" s="189" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="P24" s="227" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="Q24" s="227" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="R24" s="228"/>
       <c r="S24" s="229" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
     </row>
     <row r="25" spans="2:19">
       <c r="B25" s="65" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="C25" s="153" t="s">
         <v>155</v>
@@ -64709,34 +65665,34 @@
         <v>155</v>
       </c>
       <c r="K25" s="221" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="L25" s="221" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="M25" s="222" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="N25" s="221" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="O25" s="189" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="P25" s="227" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="Q25" s="227" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="R25" s="228"/>
       <c r="S25" s="229" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
     </row>
     <row r="26" spans="2:19">
       <c r="B26" s="65" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="C26" s="152" t="s">
         <v>155</v>
@@ -64763,34 +65719,34 @@
         <v>155</v>
       </c>
       <c r="K26" s="221" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="L26" s="221" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="M26" s="221" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="N26" s="221" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="O26" s="189" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="P26" s="227" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="Q26" s="227" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="R26" s="228"/>
       <c r="S26" s="229" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
     </row>
     <row r="27" spans="2:19">
       <c r="B27" s="65" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="C27" s="153" t="s">
         <v>155</v>
@@ -64817,34 +65773,34 @@
         <v>155</v>
       </c>
       <c r="K27" s="221" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="L27" s="221" t="s">
+        <v>292</v>
+      </c>
+      <c r="M27" s="221" t="s">
         <v>293</v>
       </c>
-      <c r="M27" s="221" t="s">
-        <v>294</v>
-      </c>
       <c r="N27" s="221" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="O27" s="189" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="P27" s="227" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="Q27" s="227" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="R27" s="228"/>
       <c r="S27" s="229" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
     </row>
     <row r="28" spans="2:19">
       <c r="B28" s="65" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="C28" s="153" t="s">
         <v>155</v>
@@ -64871,34 +65827,34 @@
         <v>155</v>
       </c>
       <c r="K28" s="221" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="L28" s="221" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="M28" s="221" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="N28" s="221" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="O28" s="189" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="P28" s="227" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="Q28" s="227" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="R28" s="228"/>
       <c r="S28" s="229" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
     </row>
     <row r="29" spans="2:19">
       <c r="B29" s="65" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="C29" s="153" t="s">
         <v>155</v>
@@ -64925,34 +65881,34 @@
         <v>155</v>
       </c>
       <c r="K29" s="221" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="L29" s="221" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="M29" s="221" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="N29" s="221" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="O29" s="189" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="P29" s="227" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="Q29" s="227" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="R29" s="228"/>
       <c r="S29" s="229" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
     </row>
     <row r="30" spans="2:19">
       <c r="B30" s="65" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="C30" s="152" t="s">
         <v>155</v>
@@ -64979,34 +65935,34 @@
         <v>155</v>
       </c>
       <c r="K30" s="221" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="L30" s="221" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="M30" s="222" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="N30" s="221" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="O30" s="189" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="P30" s="227" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="Q30" s="227" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="R30" s="228"/>
       <c r="S30" s="229" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
     </row>
     <row r="31" spans="2:19">
       <c r="B31" s="65" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="C31" s="153" t="s">
         <v>155</v>
@@ -65033,34 +65989,34 @@
         <v>155</v>
       </c>
       <c r="K31" s="221" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="L31" s="221" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="M31" s="222" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="N31" s="221" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="O31" s="189" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="P31" s="227" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="Q31" s="227" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="R31" s="228"/>
       <c r="S31" s="229" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
     </row>
     <row r="32" spans="2:19">
       <c r="B32" s="65" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="C32" s="153" t="s">
         <v>155</v>
@@ -65087,34 +66043,34 @@
         <v>155</v>
       </c>
       <c r="K32" s="221" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="L32" s="221" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="M32" s="222" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="N32" s="221" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="O32" s="189" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="P32" s="227" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="Q32" s="227" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="R32" s="228"/>
       <c r="S32" s="229" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
     </row>
     <row r="33" spans="2:19">
       <c r="B33" s="65" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="C33" s="153" t="s">
         <v>155</v>
@@ -65141,34 +66097,34 @@
         <v>155</v>
       </c>
       <c r="K33" s="221" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="L33" s="221" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="M33" s="222" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="N33" s="221" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="O33" s="189" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="P33" s="227" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="Q33" s="227" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="R33" s="228"/>
       <c r="S33" s="229" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
     </row>
     <row r="34" spans="2:19">
       <c r="B34" s="65" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="C34" s="152" t="s">
         <v>155</v>
@@ -65195,34 +66151,34 @@
         <v>155</v>
       </c>
       <c r="K34" s="221" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="L34" s="222" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="M34" s="221" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="N34" s="221" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="O34" s="189" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="P34" s="227" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="Q34" s="227" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="R34" s="228"/>
       <c r="S34" s="229" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
     </row>
     <row r="35" spans="2:19">
       <c r="B35" s="65" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="C35" s="153" t="s">
         <v>155</v>
@@ -65249,34 +66205,34 @@
         <v>155</v>
       </c>
       <c r="K35" s="221" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="L35" s="222" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="M35" s="221" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="N35" s="221" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="O35" s="189" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="P35" s="227" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="Q35" s="227" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="R35" s="228"/>
       <c r="S35" s="229" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
     </row>
     <row r="36" spans="2:19">
       <c r="B36" s="65" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="C36" s="153" t="s">
         <v>155</v>
@@ -65303,34 +66259,34 @@
         <v>155</v>
       </c>
       <c r="K36" s="221" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="L36" s="222" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="M36" s="221" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="N36" s="221" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="O36" s="189" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="P36" s="227" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="Q36" s="227" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="R36" s="228"/>
       <c r="S36" s="229" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
     </row>
     <row r="37" spans="2:19">
       <c r="B37" s="65" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="C37" s="153" t="s">
         <v>155</v>
@@ -65357,34 +66313,34 @@
         <v>155</v>
       </c>
       <c r="K37" s="221" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="L37" s="222" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="M37" s="221" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="N37" s="221" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="O37" s="189" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="P37" s="227" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="Q37" s="227" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="R37" s="228"/>
       <c r="S37" s="229" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
     </row>
     <row r="38" spans="2:19">
       <c r="B38" s="65" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="C38" s="152" t="s">
         <v>155</v>
@@ -65411,34 +66367,34 @@
         <v>155</v>
       </c>
       <c r="K38" s="221" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="L38" s="222" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="M38" s="222" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="N38" s="221" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="O38" s="189" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="P38" s="227" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="Q38" s="227" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="R38" s="228"/>
       <c r="S38" s="229" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
     </row>
     <row r="39" spans="2:19">
       <c r="B39" s="65" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="C39" s="153" t="s">
         <v>155</v>
@@ -65465,34 +66421,34 @@
         <v>155</v>
       </c>
       <c r="K39" s="221" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="L39" s="222" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="M39" s="222" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="N39" s="221" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="O39" s="189" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="P39" s="227" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="Q39" s="227" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="R39" s="228"/>
       <c r="S39" s="229" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
     </row>
     <row r="40" spans="2:19">
       <c r="B40" s="65" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="C40" s="153" t="s">
         <v>155</v>
@@ -65519,34 +66475,34 @@
         <v>155</v>
       </c>
       <c r="K40" s="221" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="L40" s="222" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="M40" s="222" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="N40" s="221" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="O40" s="189" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="P40" s="227" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="Q40" s="227" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="R40" s="228"/>
       <c r="S40" s="229" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
     </row>
     <row r="41" spans="2:19">
       <c r="B41" s="65" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="C41" s="153" t="s">
         <v>155</v>
@@ -65573,34 +66529,34 @@
         <v>155</v>
       </c>
       <c r="K41" s="221" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="L41" s="222" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="M41" s="222" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="N41" s="221" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="O41" s="189" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="P41" s="227" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="Q41" s="227" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="R41" s="228"/>
       <c r="S41" s="229" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
     </row>
-    <row r="42" spans="2:19" ht="14.25" thickBot="1">
+    <row r="42" spans="2:19" ht="13.5" thickBot="1">
       <c r="B42" s="200" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="C42" s="201" t="s">
         <v>155</v>
@@ -65627,16 +66583,16 @@
         <v>155</v>
       </c>
       <c r="K42" s="230" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="L42" s="230" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="M42" s="230" t="s">
+        <v>238</v>
+      </c>
+      <c r="N42" s="230" t="s">
         <v>239</v>
-      </c>
-      <c r="N42" s="230" t="s">
-        <v>240</v>
       </c>
       <c r="O42" s="231" t="s">
         <v>30</v>
@@ -65677,41 +66633,41 @@
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
   <dimension ref="B2:BC62"/>
-  <sheetFormatPr defaultRowHeight="13.5"/>
+  <sheetFormatPr defaultRowHeight="13"/>
   <cols>
     <col min="2" max="2" width="114" customWidth="1"/>
-    <col min="3" max="10" width="3.375" customWidth="1"/>
-    <col min="11" max="11" width="13.75" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="35.25" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="36.5" bestFit="1" customWidth="1"/>
-    <col min="14" max="15" width="19.125" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="22.375" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="16.375" customWidth="1"/>
-    <col min="18" max="18" width="25.625" customWidth="1"/>
-    <col min="19" max="19" width="24.25" bestFit="1" customWidth="1"/>
-    <col min="20" max="22" width="18.125" customWidth="1"/>
-    <col min="23" max="23" width="16.875" customWidth="1"/>
+    <col min="3" max="10" width="3.36328125" customWidth="1"/>
+    <col min="11" max="11" width="13.7265625" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="35.26953125" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="36.453125" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="19.08984375" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="22.36328125" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="16.36328125" customWidth="1"/>
+    <col min="18" max="18" width="25.6328125" customWidth="1"/>
+    <col min="19" max="19" width="24.26953125" bestFit="1" customWidth="1"/>
+    <col min="20" max="22" width="18.08984375" customWidth="1"/>
+    <col min="23" max="23" width="16.90625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:55" ht="15" thickBot="1">
+    <row r="2" spans="2:55" ht="14.5" thickBot="1">
       <c r="B2" s="260" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
     </row>
-    <row r="3" spans="2:55" ht="15" thickBot="1">
+    <row r="3" spans="2:55" ht="14.5" thickBot="1">
       <c r="B3" s="85" t="s">
         <v>123</v>
       </c>
-      <c r="C3" s="339" t="s">
-        <v>298</v>
-      </c>
-      <c r="D3" s="340"/>
-      <c r="E3" s="340"/>
-      <c r="F3" s="340"/>
-      <c r="G3" s="340"/>
-      <c r="H3" s="340"/>
-      <c r="I3" s="340"/>
-      <c r="J3" s="341"/>
+      <c r="C3" s="346" t="s">
+        <v>297</v>
+      </c>
+      <c r="D3" s="347"/>
+      <c r="E3" s="347"/>
+      <c r="F3" s="347"/>
+      <c r="G3" s="347"/>
+      <c r="H3" s="347"/>
+      <c r="I3" s="347"/>
+      <c r="J3" s="348"/>
       <c r="K3" s="154"/>
       <c r="L3" s="154"/>
       <c r="M3" s="154"/>
@@ -65723,7 +66679,7 @@
     <row r="4" spans="2:55">
       <c r="B4" s="61"/>
       <c r="C4" s="30" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="D4" s="30"/>
       <c r="E4" s="30"/>
@@ -65745,24 +66701,24 @@
       <c r="B5" s="62" t="s">
         <v>21</v>
       </c>
-      <c r="C5" s="342" t="s">
+      <c r="C5" s="349" t="s">
         <v>161</v>
       </c>
-      <c r="D5" s="343"/>
-      <c r="E5" s="343"/>
-      <c r="F5" s="343"/>
-      <c r="G5" s="343"/>
-      <c r="H5" s="343"/>
-      <c r="I5" s="343"/>
-      <c r="J5" s="344"/>
+      <c r="D5" s="350"/>
+      <c r="E5" s="350"/>
+      <c r="F5" s="350"/>
+      <c r="G5" s="350"/>
+      <c r="H5" s="350"/>
+      <c r="I5" s="350"/>
+      <c r="J5" s="351"/>
       <c r="K5" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="M5" s="31" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="N5" s="31" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="O5" s="180"/>
       <c r="P5" s="27" t="s">
@@ -65799,10 +66755,10 @@
         <v>154</v>
       </c>
       <c r="K6" s="126" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="L6" s="126" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="M6" s="126" t="s">
         <v>154</v>
@@ -65817,25 +66773,25 @@
         <v>46</v>
       </c>
     </row>
-    <row r="7" spans="2:55" ht="27">
+    <row r="7" spans="2:55" ht="26">
       <c r="B7" s="63" t="s">
         <v>26</v>
       </c>
-      <c r="C7" s="345" t="s">
+      <c r="C7" s="352" t="s">
         <v>33</v>
       </c>
-      <c r="D7" s="343"/>
-      <c r="E7" s="343"/>
-      <c r="F7" s="343"/>
-      <c r="G7" s="343"/>
-      <c r="H7" s="343"/>
-      <c r="I7" s="343"/>
-      <c r="J7" s="344"/>
+      <c r="D7" s="350"/>
+      <c r="E7" s="350"/>
+      <c r="F7" s="350"/>
+      <c r="G7" s="350"/>
+      <c r="H7" s="350"/>
+      <c r="I7" s="350"/>
+      <c r="J7" s="351"/>
       <c r="K7" s="126" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="L7" s="126" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="M7" s="126" t="s">
         <v>154</v>
@@ -65848,51 +66804,51 @@
       </c>
       <c r="P7" s="28"/>
     </row>
-    <row r="8" spans="2:55" ht="136.5">
+    <row r="8" spans="2:55" ht="131">
       <c r="B8" s="62" t="s">
         <v>27</v>
       </c>
       <c r="C8" s="150" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="D8" s="150" t="s">
         <v>60</v>
       </c>
       <c r="E8" s="150" t="s">
+        <v>198</v>
+      </c>
+      <c r="F8" s="150" t="s">
         <v>199</v>
       </c>
-      <c r="F8" s="150" t="s">
+      <c r="G8" s="150" t="s">
         <v>200</v>
       </c>
-      <c r="G8" s="150" t="s">
+      <c r="H8" s="150" t="s">
         <v>201</v>
       </c>
-      <c r="H8" s="150" t="s">
+      <c r="I8" s="150" t="s">
         <v>202</v>
       </c>
-      <c r="I8" s="150" t="s">
+      <c r="J8" s="150" t="s">
         <v>203</v>
       </c>
-      <c r="J8" s="150" t="s">
-        <v>204</v>
-      </c>
       <c r="K8" s="24" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="L8" s="24" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="M8" s="24" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="N8" s="24" t="s">
+        <v>302</v>
+      </c>
+      <c r="O8" s="202" t="s">
+        <v>222</v>
+      </c>
+      <c r="P8" s="27" t="s">
         <v>303</v>
-      </c>
-      <c r="O8" s="202" t="s">
-        <v>223</v>
-      </c>
-      <c r="P8" s="27" t="s">
-        <v>304</v>
       </c>
     </row>
     <row r="9" spans="2:55" ht="117.75" customHeight="1" thickBot="1">
@@ -65900,51 +66856,51 @@
         <v>28</v>
       </c>
       <c r="C9" s="254" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="D9" s="254" t="s">
         <v>154</v>
       </c>
       <c r="E9" s="254" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="F9" s="254" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="G9" s="254" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="H9" s="254" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="I9" s="254" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="J9" s="254" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="K9" s="182" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="L9" s="25" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="M9" s="25" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="N9" s="25" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="O9" s="25" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="P9" s="29" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
     </row>
-    <row r="10" spans="2:55" ht="14.25" thickTop="1">
+    <row r="10" spans="2:55" ht="13.5" thickTop="1">
       <c r="B10" s="65" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="C10" s="152" t="s">
         <v>155</v>
@@ -65962,7 +66918,7 @@
         <v>155</v>
       </c>
       <c r="H10" s="152" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="I10" s="152" t="s">
         <v>155</v>
@@ -65971,27 +66927,27 @@
         <v>155</v>
       </c>
       <c r="K10" s="118" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="L10" s="118" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="M10" s="32" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="N10" s="32" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="O10" s="32" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="P10" s="187" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
     </row>
     <row r="11" spans="2:55">
       <c r="B11" s="65" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="C11" s="153" t="s">
         <v>155</v>
@@ -66018,27 +66974,27 @@
         <v>155</v>
       </c>
       <c r="K11" s="118" t="s">
+        <v>207</v>
+      </c>
+      <c r="L11" s="118" t="s">
+        <v>256</v>
+      </c>
+      <c r="M11" s="118" t="s">
+        <v>344</v>
+      </c>
+      <c r="N11" s="118" t="s">
+        <v>207</v>
+      </c>
+      <c r="O11" s="118" t="s">
         <v>208</v>
       </c>
-      <c r="L11" s="118" t="s">
-        <v>257</v>
-      </c>
-      <c r="M11" s="118" t="s">
-        <v>345</v>
-      </c>
-      <c r="N11" s="118" t="s">
-        <v>208</v>
-      </c>
-      <c r="O11" s="118" t="s">
-        <v>209</v>
-      </c>
       <c r="P11" s="188" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
     </row>
     <row r="12" spans="2:55">
       <c r="B12" s="65" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="C12" s="153" t="s">
         <v>155</v>
@@ -66065,27 +67021,27 @@
         <v>155</v>
       </c>
       <c r="K12" s="118" t="s">
+        <v>207</v>
+      </c>
+      <c r="L12" s="118" t="s">
+        <v>256</v>
+      </c>
+      <c r="M12" s="118" t="s">
+        <v>344</v>
+      </c>
+      <c r="N12" s="118" t="s">
         <v>208</v>
       </c>
-      <c r="L12" s="118" t="s">
-        <v>257</v>
-      </c>
-      <c r="M12" s="118" t="s">
-        <v>345</v>
-      </c>
-      <c r="N12" s="118" t="s">
-        <v>209</v>
-      </c>
       <c r="O12" s="118" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="P12" s="188" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
     </row>
     <row r="13" spans="2:55">
       <c r="B13" s="65" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="C13" s="153" t="s">
         <v>155</v>
@@ -66112,27 +67068,27 @@
         <v>155</v>
       </c>
       <c r="K13" s="118" t="s">
+        <v>207</v>
+      </c>
+      <c r="L13" s="118" t="s">
+        <v>256</v>
+      </c>
+      <c r="M13" s="118" t="s">
+        <v>344</v>
+      </c>
+      <c r="N13" s="118" t="s">
         <v>208</v>
       </c>
-      <c r="L13" s="118" t="s">
-        <v>257</v>
-      </c>
-      <c r="M13" s="118" t="s">
-        <v>345</v>
-      </c>
-      <c r="N13" s="118" t="s">
-        <v>209</v>
-      </c>
       <c r="O13" s="118" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="P13" s="188" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
     </row>
     <row r="14" spans="2:55">
       <c r="B14" s="65" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="C14" s="152" t="s">
         <v>155</v>
@@ -66159,27 +67115,27 @@
         <v>155</v>
       </c>
       <c r="K14" s="118" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="L14" s="118" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="M14" s="118" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="N14" s="118" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="O14" s="118" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="P14" s="188" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
     </row>
     <row r="15" spans="2:55">
       <c r="B15" s="65" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="C15" s="153" t="s">
         <v>155</v>
@@ -66206,27 +67162,27 @@
         <v>155</v>
       </c>
       <c r="K15" s="118" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="L15" s="118" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="M15" s="118" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="N15" s="118" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="O15" s="118" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="P15" s="188" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
     </row>
     <row r="16" spans="2:55">
       <c r="B16" s="65" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="C16" s="153" t="s">
         <v>155</v>
@@ -66253,27 +67209,27 @@
         <v>155</v>
       </c>
       <c r="K16" s="118" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="L16" s="118" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="M16" s="118" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="N16" s="118" t="s">
+        <v>217</v>
+      </c>
+      <c r="O16" s="118" t="s">
         <v>218</v>
       </c>
-      <c r="O16" s="118" t="s">
-        <v>219</v>
-      </c>
       <c r="P16" s="188" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
     </row>
     <row r="17" spans="2:16">
       <c r="B17" s="65" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="C17" s="153" t="s">
         <v>155</v>
@@ -66300,27 +67256,27 @@
         <v>155</v>
       </c>
       <c r="K17" s="118" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="L17" s="118" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="M17" s="118" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="N17" s="118" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="O17" s="118" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="P17" s="188" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
     </row>
     <row r="18" spans="2:16">
       <c r="B18" s="65" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="C18" s="153" t="s">
         <v>155</v>
@@ -66347,27 +67303,27 @@
         <v>155</v>
       </c>
       <c r="K18" s="118" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="L18" s="118" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="M18" s="118" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="N18" s="118" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="O18" s="118" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="P18" s="188" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
     </row>
     <row r="19" spans="2:16">
       <c r="B19" s="65" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="C19" s="153" t="s">
         <v>155</v>
@@ -66394,27 +67350,27 @@
         <v>155</v>
       </c>
       <c r="K19" s="118" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="L19" s="118" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="M19" s="118" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="N19" s="118" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="O19" s="118" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="P19" s="188" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
     </row>
     <row r="20" spans="2:16">
       <c r="B20" s="65" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="C20" s="153" t="s">
         <v>155</v>
@@ -66441,27 +67397,27 @@
         <v>155</v>
       </c>
       <c r="K20" s="118" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="L20" s="118" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="M20" s="118" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="N20" s="118" t="s">
+        <v>217</v>
+      </c>
+      <c r="O20" s="118" t="s">
         <v>218</v>
       </c>
-      <c r="O20" s="118" t="s">
-        <v>219</v>
-      </c>
       <c r="P20" s="188" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
     </row>
     <row r="21" spans="2:16">
       <c r="B21" s="65" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="C21" s="153" t="s">
         <v>155</v>
@@ -66488,27 +67444,27 @@
         <v>155</v>
       </c>
       <c r="K21" s="118" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="L21" s="118" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="M21" s="118" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="N21" s="118" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="O21" s="118" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="P21" s="188" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
     </row>
     <row r="22" spans="2:16">
       <c r="B22" s="65" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="C22" s="153" t="s">
         <v>155</v>
@@ -66535,27 +67491,27 @@
         <v>155</v>
       </c>
       <c r="K22" s="118" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="L22" s="118" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="M22" s="118" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="N22" s="118" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="O22" s="118" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="P22" s="188" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
     </row>
     <row r="23" spans="2:16">
       <c r="B23" s="65" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="C23" s="153" t="s">
         <v>155</v>
@@ -66582,27 +67538,27 @@
         <v>155</v>
       </c>
       <c r="K23" s="118" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="L23" s="118" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="M23" s="118" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="N23" s="118" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="O23" s="118" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="P23" s="188" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
     </row>
     <row r="24" spans="2:16">
       <c r="B24" s="65" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="C24" s="153" t="s">
         <v>155</v>
@@ -66629,27 +67585,27 @@
         <v>155</v>
       </c>
       <c r="K24" s="118" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="L24" s="118" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="M24" s="118" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="N24" s="118" t="s">
+        <v>217</v>
+      </c>
+      <c r="O24" s="118" t="s">
         <v>218</v>
       </c>
-      <c r="O24" s="118" t="s">
-        <v>219</v>
-      </c>
       <c r="P24" s="188" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
     </row>
     <row r="25" spans="2:16">
       <c r="B25" s="65" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="C25" s="153" t="s">
         <v>155</v>
@@ -66676,27 +67632,27 @@
         <v>155</v>
       </c>
       <c r="K25" s="118" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="L25" s="118" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="M25" s="118" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="N25" s="118" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="O25" s="118" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="P25" s="188" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
     </row>
     <row r="26" spans="2:16">
       <c r="B26" s="65" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="C26" s="153" t="s">
         <v>155</v>
@@ -66723,27 +67679,27 @@
         <v>155</v>
       </c>
       <c r="K26" s="33" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="L26" s="33" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="M26" s="33" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="N26" s="33" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="O26" s="33" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="P26" s="199" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
     </row>
     <row r="27" spans="2:16">
       <c r="B27" s="65" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="C27" s="153" t="s">
         <v>155</v>
@@ -66770,27 +67726,27 @@
         <v>155</v>
       </c>
       <c r="K27" s="33" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="L27" s="33" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="M27" s="33" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="N27" s="33" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="O27" s="33" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="P27" s="199" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
     </row>
     <row r="28" spans="2:16">
       <c r="B28" s="65" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="C28" s="153" t="s">
         <v>155</v>
@@ -66817,27 +67773,27 @@
         <v>155</v>
       </c>
       <c r="K28" s="33" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="L28" s="33" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="M28" s="33" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="N28" s="33" t="s">
+        <v>217</v>
+      </c>
+      <c r="O28" s="33" t="s">
         <v>218</v>
       </c>
-      <c r="O28" s="33" t="s">
-        <v>219</v>
-      </c>
       <c r="P28" s="199" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
     </row>
     <row r="29" spans="2:16">
       <c r="B29" s="65" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="C29" s="153" t="s">
         <v>155</v>
@@ -66864,27 +67820,27 @@
         <v>155</v>
       </c>
       <c r="K29" s="33" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="L29" s="33" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="M29" s="33" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="N29" s="33" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="O29" s="33" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="P29" s="199" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
     </row>
     <row r="30" spans="2:16">
       <c r="B30" s="65" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="C30" s="153" t="s">
         <v>155</v>
@@ -66911,27 +67867,27 @@
         <v>155</v>
       </c>
       <c r="K30" s="118" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="L30" s="118" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="M30" s="118" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="N30" s="118" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="O30" s="32" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="P30" s="188" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
     </row>
     <row r="31" spans="2:16">
       <c r="B31" s="65" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="C31" s="153" t="s">
         <v>155</v>
@@ -66958,27 +67914,27 @@
         <v>155</v>
       </c>
       <c r="K31" s="118" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="L31" s="118" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="M31" s="118" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="N31" s="118" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="O31" s="32" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="P31" s="188" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
     </row>
     <row r="32" spans="2:16">
       <c r="B32" s="65" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="C32" s="153" t="s">
         <v>155</v>
@@ -67005,27 +67961,27 @@
         <v>155</v>
       </c>
       <c r="K32" s="118" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="L32" s="118" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="M32" s="118" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="N32" s="118" t="s">
+        <v>217</v>
+      </c>
+      <c r="O32" s="118" t="s">
         <v>218</v>
       </c>
-      <c r="O32" s="118" t="s">
-        <v>219</v>
-      </c>
       <c r="P32" s="188" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
     </row>
     <row r="33" spans="2:54">
       <c r="B33" s="65" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="C33" s="153" t="s">
         <v>155</v>
@@ -67052,27 +68008,27 @@
         <v>155</v>
       </c>
       <c r="K33" s="118" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="L33" s="118" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="M33" s="118" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="N33" s="118" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="O33" s="118" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="P33" s="188" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
     </row>
     <row r="34" spans="2:54">
       <c r="B34" s="65" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="C34" s="152" t="s">
         <v>155</v>
@@ -67099,27 +68055,27 @@
         <v>155</v>
       </c>
       <c r="K34" s="118" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="L34" s="118" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="M34" s="118" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="N34" s="118" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="O34" s="118" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="P34" s="188" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
     </row>
     <row r="35" spans="2:54">
       <c r="B35" s="65" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="C35" s="153" t="s">
         <v>155</v>
@@ -67146,27 +68102,27 @@
         <v>155</v>
       </c>
       <c r="K35" s="118" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="L35" s="118" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="M35" s="118" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="N35" s="118" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="O35" s="118" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="P35" s="188" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
     </row>
     <row r="36" spans="2:54">
       <c r="B36" s="65" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="C36" s="153" t="s">
         <v>155</v>
@@ -67193,27 +68149,27 @@
         <v>155</v>
       </c>
       <c r="K36" s="118" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="L36" s="118" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="M36" s="118" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="N36" s="118" t="s">
+        <v>217</v>
+      </c>
+      <c r="O36" s="118" t="s">
         <v>218</v>
       </c>
-      <c r="O36" s="118" t="s">
-        <v>219</v>
-      </c>
       <c r="P36" s="188" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
     </row>
     <row r="37" spans="2:54">
       <c r="B37" s="65" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="C37" s="153" t="s">
         <v>155</v>
@@ -67240,27 +68196,27 @@
         <v>155</v>
       </c>
       <c r="K37" s="118" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="L37" s="118" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="M37" s="118" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="N37" s="118" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="O37" s="118" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="P37" s="188" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
     </row>
     <row r="38" spans="2:54">
       <c r="B38" s="246" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="C38" s="247" t="s">
         <v>155</v>
@@ -67287,27 +68243,27 @@
         <v>155</v>
       </c>
       <c r="K38" s="248" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="L38" s="248" t="s">
+        <v>238</v>
+      </c>
+      <c r="M38" s="118" t="s">
+        <v>346</v>
+      </c>
+      <c r="N38" s="248" t="s">
         <v>239</v>
       </c>
-      <c r="M38" s="118" t="s">
-        <v>347</v>
-      </c>
-      <c r="N38" s="248" t="s">
-        <v>240</v>
-      </c>
       <c r="O38" s="241" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="P38" s="249" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
     </row>
-    <row r="39" spans="2:54" ht="14.25" thickBot="1">
+    <row r="39" spans="2:54" ht="13.5" thickBot="1">
       <c r="B39" s="250" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="C39" s="201" t="s">
         <v>155</v>
@@ -67334,43 +68290,43 @@
         <v>155</v>
       </c>
       <c r="K39" s="239" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="L39" s="239" t="s">
+        <v>238</v>
+      </c>
+      <c r="M39" s="239" t="s">
+        <v>344</v>
+      </c>
+      <c r="N39" s="239" t="s">
         <v>239</v>
       </c>
-      <c r="M39" s="239" t="s">
-        <v>345</v>
-      </c>
-      <c r="N39" s="239" t="s">
-        <v>240</v>
-      </c>
       <c r="O39" s="240" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="P39" s="238" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
     </row>
-    <row r="46" spans="2:54" ht="15" thickBot="1">
+    <row r="46" spans="2:54" ht="14.5" thickBot="1">
       <c r="B46" s="260" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
     </row>
-    <row r="47" spans="2:54" ht="15" thickBot="1">
+    <row r="47" spans="2:54" ht="14.5" thickBot="1">
       <c r="B47" s="85" t="s">
         <v>123</v>
       </c>
-      <c r="C47" s="339" t="s">
-        <v>298</v>
-      </c>
-      <c r="D47" s="340"/>
-      <c r="E47" s="340"/>
-      <c r="F47" s="340"/>
-      <c r="G47" s="340"/>
-      <c r="H47" s="340"/>
-      <c r="I47" s="340"/>
-      <c r="J47" s="341"/>
+      <c r="C47" s="346" t="s">
+        <v>297</v>
+      </c>
+      <c r="D47" s="347"/>
+      <c r="E47" s="347"/>
+      <c r="F47" s="347"/>
+      <c r="G47" s="347"/>
+      <c r="H47" s="347"/>
+      <c r="I47" s="347"/>
+      <c r="J47" s="348"/>
       <c r="K47" s="154"/>
       <c r="L47" s="154"/>
       <c r="M47" s="154"/>
@@ -67380,7 +68336,7 @@
     <row r="48" spans="2:54">
       <c r="B48" s="61"/>
       <c r="C48" s="30" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="D48" s="30"/>
       <c r="E48" s="30"/>
@@ -67400,21 +68356,21 @@
       <c r="B49" s="62" t="s">
         <v>21</v>
       </c>
-      <c r="C49" s="342" t="s">
+      <c r="C49" s="349" t="s">
         <v>161</v>
       </c>
-      <c r="D49" s="343"/>
-      <c r="E49" s="343"/>
-      <c r="F49" s="343"/>
-      <c r="G49" s="343"/>
-      <c r="H49" s="343"/>
-      <c r="I49" s="343"/>
-      <c r="J49" s="344"/>
+      <c r="D49" s="350"/>
+      <c r="E49" s="350"/>
+      <c r="F49" s="350"/>
+      <c r="G49" s="350"/>
+      <c r="H49" s="350"/>
+      <c r="I49" s="350"/>
+      <c r="J49" s="351"/>
       <c r="K49" s="193" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="L49" s="235" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="M49" s="203"/>
       <c r="N49" s="27" t="s">
@@ -67463,20 +68419,20 @@
         <v>46</v>
       </c>
     </row>
-    <row r="51" spans="2:54" ht="27">
+    <row r="51" spans="2:54" ht="26">
       <c r="B51" s="63" t="s">
         <v>26</v>
       </c>
-      <c r="C51" s="345" t="s">
+      <c r="C51" s="352" t="s">
         <v>33</v>
       </c>
-      <c r="D51" s="343"/>
-      <c r="E51" s="343"/>
-      <c r="F51" s="343"/>
-      <c r="G51" s="343"/>
-      <c r="H51" s="343"/>
-      <c r="I51" s="343"/>
-      <c r="J51" s="344"/>
+      <c r="D51" s="350"/>
+      <c r="E51" s="350"/>
+      <c r="F51" s="350"/>
+      <c r="G51" s="350"/>
+      <c r="H51" s="350"/>
+      <c r="I51" s="350"/>
+      <c r="J51" s="351"/>
       <c r="K51" s="207" t="s">
         <v>154</v>
       </c>
@@ -67488,48 +68444,48 @@
       </c>
       <c r="N51" s="28"/>
     </row>
-    <row r="52" spans="2:54" ht="136.5">
+    <row r="52" spans="2:54" ht="131">
       <c r="B52" s="62" t="s">
         <v>27</v>
       </c>
       <c r="C52" s="150" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="D52" s="150" t="s">
         <v>60</v>
       </c>
       <c r="E52" s="150" t="s">
+        <v>198</v>
+      </c>
+      <c r="F52" s="150" t="s">
         <v>199</v>
       </c>
-      <c r="F52" s="150" t="s">
+      <c r="G52" s="150" t="s">
         <v>200</v>
       </c>
-      <c r="G52" s="150" t="s">
+      <c r="H52" s="150" t="s">
         <v>201</v>
       </c>
-      <c r="H52" s="150" t="s">
+      <c r="I52" s="150" t="s">
         <v>202</v>
       </c>
-      <c r="I52" s="150" t="s">
+      <c r="J52" s="150" t="s">
         <v>203</v>
       </c>
-      <c r="J52" s="150" t="s">
-        <v>204</v>
-      </c>
       <c r="K52" s="212" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="L52" s="212" t="s">
+        <v>302</v>
+      </c>
+      <c r="M52" s="212" t="s">
+        <v>222</v>
+      </c>
+      <c r="N52" s="27" t="s">
         <v>303</v>
       </c>
-      <c r="M52" s="212" t="s">
-        <v>223</v>
-      </c>
-      <c r="N52" s="27" t="s">
-        <v>304</v>
-      </c>
       <c r="O52" s="179" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
     </row>
     <row r="53" spans="2:54" ht="117.75" customHeight="1" thickBot="1">
@@ -67537,45 +68493,45 @@
         <v>28</v>
       </c>
       <c r="C53" s="254" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="D53" s="254" t="s">
         <v>154</v>
       </c>
       <c r="E53" s="254" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="F53" s="254" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="G53" s="254" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="H53" s="254" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="I53" s="254" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="J53" s="254" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="K53" s="215" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="L53" s="215" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="M53" s="216" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="N53" s="29" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
     </row>
-    <row r="54" spans="2:54" ht="14.25" thickTop="1">
+    <row r="54" spans="2:54" ht="13.5" thickTop="1">
       <c r="B54" s="65" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="C54" s="152" t="s">
         <v>155</v>
@@ -67602,21 +68558,21 @@
         <v>155</v>
       </c>
       <c r="K54" s="221" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="L54" s="221" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="M54" s="221" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="N54" s="236" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
     </row>
     <row r="55" spans="2:54">
       <c r="B55" s="65" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="C55" s="153" t="s">
         <v>155</v>
@@ -67643,21 +68599,21 @@
         <v>155</v>
       </c>
       <c r="K55" s="221" t="s">
+        <v>207</v>
+      </c>
+      <c r="L55" s="221" t="s">
+        <v>207</v>
+      </c>
+      <c r="M55" s="221" t="s">
         <v>208</v>
       </c>
-      <c r="L55" s="221" t="s">
-        <v>208</v>
-      </c>
-      <c r="M55" s="221" t="s">
-        <v>209</v>
-      </c>
       <c r="N55" s="188" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
     </row>
     <row r="56" spans="2:54">
       <c r="B56" s="65" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="C56" s="153" t="s">
         <v>155</v>
@@ -67684,21 +68640,21 @@
         <v>155</v>
       </c>
       <c r="K56" s="222" t="s">
+        <v>207</v>
+      </c>
+      <c r="L56" s="222" t="s">
         <v>208</v>
       </c>
-      <c r="L56" s="222" t="s">
-        <v>209</v>
-      </c>
       <c r="M56" s="222" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="N56" s="188" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
     </row>
     <row r="57" spans="2:54">
       <c r="B57" s="65" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="C57" s="153" t="s">
         <v>155</v>
@@ -67725,21 +68681,21 @@
         <v>155</v>
       </c>
       <c r="K57" s="222" t="s">
+        <v>207</v>
+      </c>
+      <c r="L57" s="222" t="s">
         <v>208</v>
       </c>
-      <c r="L57" s="222" t="s">
-        <v>209</v>
-      </c>
       <c r="M57" s="222" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="N57" s="188" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
     </row>
     <row r="58" spans="2:54">
       <c r="B58" s="65" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="C58" s="152" t="s">
         <v>155</v>
@@ -67766,21 +68722,21 @@
         <v>155</v>
       </c>
       <c r="K58" s="222" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="L58" s="222" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="M58" s="222" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="N58" s="188" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
     </row>
     <row r="59" spans="2:54">
       <c r="B59" s="65" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="C59" s="153" t="s">
         <v>155</v>
@@ -67807,21 +68763,21 @@
         <v>155</v>
       </c>
       <c r="K59" s="222" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="L59" s="222" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="M59" s="222" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="N59" s="188" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
     </row>
     <row r="60" spans="2:54">
       <c r="B60" s="237" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="C60" s="153" t="s">
         <v>155</v>
@@ -67848,21 +68804,21 @@
         <v>155</v>
       </c>
       <c r="K60" s="256" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="L60" s="256" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="M60" s="256" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="N60" s="188" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
     </row>
     <row r="61" spans="2:54">
       <c r="B61" s="252" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="C61" s="247" t="s">
         <v>155</v>
@@ -67889,21 +68845,21 @@
         <v>155</v>
       </c>
       <c r="K61" s="257" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="L61" s="257" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="M61" s="257" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="N61" s="249" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
     </row>
-    <row r="62" spans="2:54" ht="14.25" thickBot="1">
+    <row r="62" spans="2:54" ht="13.5" thickBot="1">
       <c r="B62" s="250" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="C62" s="253" t="s">
         <v>155</v>
@@ -67930,16 +68886,16 @@
         <v>155</v>
       </c>
       <c r="K62" s="230" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="L62" s="230" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="M62" s="230" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="N62" s="238" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
     </row>
   </sheetData>
